--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -660,49 +660,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 261026억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 261025억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 262360억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 263179억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 261074억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 261873억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 258876억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 259656억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 256251억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 257012억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 253966억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 253887억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 250335억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 250257억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 245670억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 245591억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -912,37 +912,37 @@
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3476억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3477억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3682억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3683억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3915억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 3916억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4167억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4169억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4184억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4186억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4402억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 4404억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1707,49 +1707,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 261026억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 261025억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 262360억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 263179억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 261074억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 261873억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 258876억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 259656억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 256251억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 257012억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 253966억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 253887억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 250335억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 250257억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 245670억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 245591억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2174,37 +2174,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3476억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3477억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3682억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3683억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3915억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 3916억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4167억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4169억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4184억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4186억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4402억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 4404억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -6319,33 +6319,33 @@
         <v>0.252843</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.416668</v>
+        <v>0.416661</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.318587</v>
+        <v>0.318582</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.303859</v>
+        <v>0.307925</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.086129</v>
+        <v>0.089453</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.016987</v>
+        <v>0.020054</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.018293</v>
+        <v>-0.015371</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.031993</v>
+        <v>-0.035302</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.041129</v>
+        <v>-0.044358</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.051014</v>
+        <v>-0.054167</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6472,32 +6472,32 @@
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.108091</v>
+        <v>0.108092</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.108092</v>
+        <v>0.108093</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.10809</v>
+        <v>0.108095</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.108093</v>
+        <v>0.108094</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
+        <v>0.108092</v>
+      </c>
+      <c r="AL22" s="24" t="n">
         <v>0.108093</v>
       </c>
-      <c r="AL22" s="24" t="n">
-        <v>0.108094</v>
-      </c>
       <c r="AM22" s="24" t="n">
-        <v>0.108095</v>
+        <v>0.10809</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.108091</v>
+        <v>0.108092</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6620,20 +6620,20 @@
         <v>0.070673</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.070678</v>
+        <v>0.070674</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.070678</v>
+        <v>0.070674</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.070676</v>
+        <v>0.070675</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.070678</v>
+        <v>0.070675</v>
       </c>
       <c r="AI23" s="24" t="n">
         <v>0.070675</v>
@@ -6646,13 +6646,13 @@
         <v>0.070677</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.070676</v>
+        <v>0.070673</v>
       </c>
       <c r="AM23" s="24" t="n">
         <v>0.070673</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.070675</v>
+        <v>0.070674</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -6907,26 +6907,26 @@
         <v>92.16</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>92.28</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>97.73999999999999</v>
+        <v>97.77</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>103.91</v>
+        <v>103.95</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>110.61</v>
+        <v>110.66</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>111.06</v>
+        <v>111.11</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>116.85</v>
+        <v>116.9</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7214,23 +7214,23 @@
         <v>0.084148</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.08412</v>
+        <v>0.08412500000000001</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.084152</v>
+        <v>0.084129</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.084121</v>
+        <v>0.084117</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.084138</v>
+        <v>0.084118</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.084149</v>
+        <v>0.084146</v>
       </c>
       <c r="AM27" s="24" t="n">
         <v>0.08414199999999999</v>
@@ -7369,26 +7369,26 @@
         <v>0.926756</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.926714</v>
+        <v>0.926763</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.926719</v>
+        <v>0.9267570000000001</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.9267339999999999</v>
+        <v>0.926747</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.926752</v>
+        <v>0.926739</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.926713</v>
+        <v>0.926756</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.926741</v>
+        <v>0.926698</v>
       </c>
       <c r="AN28" s="24" t="n">
         <v>0.926767</v>
@@ -7759,23 +7759,23 @@
         <v>0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>216.02</v>
+        <v>216.03</v>
       </c>
       <c r="AH31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>216.01</v>
+        <v>216.03</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AN31" s="29" t="n">
         <v>0.01</v>
@@ -8103,26 +8103,26 @@
         <v>0.073855</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.001253</v>
+        <v>0.001374</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.059234</v>
+        <v>0.059336</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.063124</v>
+        <v>0.063232</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.064482</v>
+        <v>0.06458899999999999</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.004053</v>
+        <v>0.004054</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.052134</v>
+        <v>0.052112</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.055123</v>
+        <v>0.055101</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8880,7 +8880,7 @@
         <v>-0.432432</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>-0.462185</v>
+        <v>-0.470588</v>
       </c>
       <c r="AH41" s="24" t="n">
         <v>-0.15493</v>
@@ -8893,7 +8893,7 @@
         <v>-0.142857</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>-0.15625</v>
+        <v>-0.142857</v>
       </c>
       <c r="AM41" s="24" t="n">
         <v>-0.133333</v>
@@ -9174,20 +9174,20 @@
         <v>0.070673</v>
       </c>
       <c r="AD43" s="24" t="n">
-        <v>0.070678</v>
+        <v>0.070674</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE34/subQ!AE33,"")</f>
         <v/>
       </c>
       <c r="AF43" s="24" t="n">
-        <v>0.070678</v>
+        <v>0.070674</v>
       </c>
       <c r="AG43" s="24" t="n">
-        <v>0.070676</v>
+        <v>0.070675</v>
       </c>
       <c r="AH43" s="24" t="n">
-        <v>0.070678</v>
+        <v>0.070675</v>
       </c>
       <c r="AI43" s="24" t="n">
         <v>0.070675</v>
@@ -9200,13 +9200,13 @@
         <v>0.070677</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>0.070676</v>
+        <v>0.070673</v>
       </c>
       <c r="AM43" s="24" t="n">
         <v>0.070673</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>0.070675</v>
+        <v>0.070674</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO34/subQ!AO33,"")</f>
@@ -38270,7 +38270,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2564.3</v>
+        <v>2565.5</v>
       </c>
     </row>
     <row r="30">
@@ -38310,7 +38310,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2566</v>
+        <v>0.2567</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$98</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$104</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$84</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -648,61 +648,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 240370억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+전년동기 × (1+17.3%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 254552억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+전년동기 × (1+17.3%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 261025억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+전년동기 × (1+17.3%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263179억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+전년동기 × (1+17.3%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 261873억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+전년동기 × (1+8.6%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 259656억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+전년동기 × (1+8.6%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 257012억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+전년동기 × (1+8.6%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 253887억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+전년동기 × (1+8.6%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 250257억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+전년동기 × (1+4.3%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 245591억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+전년동기 × (1+4.3%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -768,181 +768,181 @@
     <comment ref="AC23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AD23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AG23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AH23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AI23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AK23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AL23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AM23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AN23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 7.1% 유지</t>
+최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AD24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 7.1% 유지</t>
+최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AF24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 7.1% 유지</t>
+최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 7.1% 유지</t>
+최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AH24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 7.1% 유지</t>
+최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AI24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 7.1% 유지</t>
+최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AK24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 7.1% 유지</t>
+최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AL24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 7.1% 유지</t>
+최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AM24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 7.1% 유지</t>
+최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AN24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 7.1% 유지</t>
+최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AC25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2839억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2839억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3019억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1322억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3233억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -222억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3472억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -1779억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3477억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -3615억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3683억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -5293억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 3916억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -7001억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4169억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -8724억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4186억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -10733억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 4404억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -12595억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1305,6 +1305,126 @@
 전분기 + 지배주주순이익 − 배당</t>
       </text>
     </comment>
+    <comment ref="AC32" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AD32" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AF32" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AG32" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AH32" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AI32" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AK32" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AL32" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AM32" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AN32" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AC33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AD33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AF33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AG33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AH33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AI33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AK33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AL33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AM33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AN33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
     <comment ref="AC34" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
@@ -1443,66 +1563,6 @@
 직전 결산 DPS 700원 유지</t>
       </text>
     </comment>
-    <comment ref="AC40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AD40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AF40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AG40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AH40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AI40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AK40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AL40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AM40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AN40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ TTM EPS(추정 포함)</t>
-      </text>
-    </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
@@ -1510,54 +1570,6 @@
       </text>
     </comment>
     <comment ref="AD41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AF41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AG41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AH41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AI41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AK41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AL41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AM41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-현재 종가 ÷ BPS(추정 포함)</t>
-      </text>
-    </comment>
-    <comment ref="AN41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
 현재 종가 ÷ BPS(추정 포함)</t>
@@ -1695,61 +1707,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 240370억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 전년동기 × (1+17.3%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 254552억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 전년동기 × (1+17.3%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 261025억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 전년동기 × (1+17.3%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263179억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 전년동기 × (1+17.3%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 261873억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 전년동기 × (1+8.6%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 259656억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 전년동기 × (1+8.6%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 257012억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 전년동기 × (1+8.6%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 253887억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 전년동기 × (1+8.6%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 250257억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 전년동기 × (1+4.3%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 245591억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 전년동기 × (1+4.3%) — g=최근 4분기 합 YoY 17.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
@@ -1935,61 +1947,61 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
@@ -2090,121 +2102,121 @@
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 7.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 7.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 7.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 7.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 7.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 7.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 7.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 7.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 7.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 7.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 7.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2839억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2839억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3019억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1322억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3233억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -222억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3472억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -1779억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3477억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -3615억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3683억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -5293억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 3916억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -7001억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4169억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -8724억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4186억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -10733억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 4404억 × 10.62% − 총차입금 0억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -12595억 × 10.62% − 총차입금 18519억 × 36.85% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -2748,6 +2760,126 @@
 [roll]</t>
       </text>
     </comment>
+    <comment ref="AC21" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AD21" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AF21" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AG21" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AH21" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AI21" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AK21" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AL21" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AM21" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AN21" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AC22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AD22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AF22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AG22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AH22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AI22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AK22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AL22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AM22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AN22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
     <comment ref="AC23" authorId="0" shapeId="0">
       <text>
         <t>추정: 전분기 + (순이익 − 배당) — 순차입금 롤과 같은 가정
@@ -3301,66 +3433,6 @@
         <t>실측(계정 매핑 없음 — 모델값 직접) — 토스 일봉 분기 평균 ÷ TTM EPS</t>
       </text>
     </comment>
-    <comment ref="AC31" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AD31" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AF31" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AG31" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AH31" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AI31" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AK31" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AL31" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AM31" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AN31" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ TTM EPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
     <comment ref="E32" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — 토스 일봉 분기 평균 ÷ BPS</t>
@@ -3468,54 +3540,6 @@
       </text>
     </comment>
     <comment ref="AD32" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AF32" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AG32" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AH32" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AI32" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AK32" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AL32" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AM32" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 현재 종가 ÷ BPS(추정 포함)
-[yoy]</t>
-      </text>
-    </comment>
-    <comment ref="AN32" authorId="0" shapeId="0">
       <text>
         <t>추정: 현재 종가 ÷ BPS(추정 포함)
 [yoy]</t>
@@ -4140,7 +4164,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4261,14 +4285,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 13.1% &gt; 추세 11.9% × 1.10 (suppliers_mentions·시차 0·4분기 이동합·창 8, r=0.94 유의)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.9, "op_wape_pct": 94.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 1351.87, "rev_act": 1378.33, "op_pred": 91.64, "op_act": 155.57}, {"q": "2025Q4", "rev_pred": 1410.38, "rev_act": 1532.55, "op_pred": 95.61, "op_act": -47.06}, {"q": "2026Q1", "rev_pred": 1378.1, "rev_act": 1876.83, "op_pred": 93.42, "op_act": 281.88}, {"q": "2026Q2", "rev_pred": 1724.71, "rev_act": 1610.93, "op_pred": 116.91, "op_act": 27.93}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.9, "op_wape_pct": 94.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"wape_link": null, "wape_trend": null, "adopted": false, "note": "유의성 조건 미달 → OOS 비교 전 기각"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 1351.87, "rev_act": 1378.33, "op_pred": 91.64, "op_act": 155.57}, {"q": "2025Q4", "rev_pred": 1410.38, "rev_act": 1532.55, "op_pred": 95.61, "op_act": -47.06}, {"q": "2026Q1", "rev_pred": 1378.1, "rev_act": 1876.83, "op_pred": 93.42, "op_act": 281.88}, {"q": "2026Q2", "rev_pred": 1724.71, "rev_act": 1610.93, "op_pred": 116.91, "op_act": 27.93}]}</t>
         </is>
       </c>
     </row>
@@ -6316,36 +6340,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.252843</v>
+        <v>0.172586</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.416661</v>
+        <v>0.172585</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.318582</v>
+        <v>0.172585</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.307925</v>
+        <v>0.172587</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.089453</v>
+        <v>0.086294</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.020054</v>
+        <v>0.086297</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.015371</v>
+        <v>0.086294</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.035302</v>
+        <v>0.08629100000000001</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.044358</v>
+        <v>0.043146</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.054167</v>
+        <v>0.043148</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6462,26 +6486,26 @@
         <v/>
       </c>
       <c r="AC22" s="24" t="n">
+        <v>0.108092</v>
+      </c>
+      <c r="AD22" s="24" t="n">
         <v>0.108094</v>
-      </c>
-      <c r="AD22" s="24" t="n">
-        <v>0.108092</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.108092</v>
+        <v>0.108091</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.108093</v>
+        <v>0.108091</v>
       </c>
       <c r="AH22" s="24" t="n">
         <v>0.108095</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.108094</v>
+        <v>0.108092</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
@@ -6491,13 +6515,13 @@
         <v>0.108092</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.108093</v>
+        <v>0.108092</v>
       </c>
       <c r="AM22" s="24" t="n">
         <v>0.10809</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.108092</v>
+        <v>0.108095</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6617,42 +6641,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.070673</v>
+        <v>0.070678</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.070674</v>
+        <v>0.070677</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
+        <v>0.070676</v>
+      </c>
+      <c r="AG23" s="24" t="n">
         <v>0.070674</v>
       </c>
-      <c r="AG23" s="24" t="n">
-        <v>0.070675</v>
-      </c>
       <c r="AH23" s="24" t="n">
-        <v>0.070675</v>
+        <v>0.070673</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.070675</v>
+        <v>0.070677</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
+        <v>0.070675</v>
+      </c>
+      <c r="AL23" s="24" t="n">
+        <v>0.070674</v>
+      </c>
+      <c r="AM23" s="24" t="n">
         <v>0.070677</v>
       </c>
-      <c r="AL23" s="24" t="n">
-        <v>0.070673</v>
-      </c>
-      <c r="AM23" s="24" t="n">
-        <v>0.070673</v>
-      </c>
       <c r="AN23" s="24" t="n">
-        <v>0.070674</v>
+        <v>0.070675</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -6891,42 +6915,42 @@
         <v/>
       </c>
       <c r="AC25" s="29" t="n">
-        <v>75.34999999999999</v>
+        <v>-1630.81</v>
       </c>
       <c r="AD25" s="29" t="n">
-        <v>80.15000000000001</v>
+        <v>-1671.07</v>
       </c>
       <c r="AE25" s="30">
         <f>subQ!AE11</f>
         <v/>
       </c>
       <c r="AF25" s="29" t="n">
-        <v>85.81999999999999</v>
+        <v>-1712.06</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>92.16</v>
+        <v>-1753.37</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>92.29000000000001</v>
+        <v>-1802.1</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>97.77</v>
+        <v>-1846.65</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>103.95</v>
+        <v>-1892</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>110.66</v>
+        <v>-1937.74</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>111.11</v>
+        <v>-1991.06</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>116.9</v>
+        <v>-2040.47</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7201,42 +7225,42 @@
         <v/>
       </c>
       <c r="AC27" s="24" t="n">
-        <v>0.084148</v>
+        <v>-0</v>
       </c>
       <c r="AD27" s="24" t="n">
-        <v>0.084122</v>
+        <v>-0</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE14/subQ!AE13,"")</f>
         <v/>
       </c>
       <c r="AF27" s="24" t="n">
-        <v>0.084148</v>
+        <v>-0</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.08412500000000001</v>
+        <v>-0</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.084129</v>
+        <v>-0</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.084117</v>
+        <v>-0</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.084118</v>
+        <v>-0</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.084146</v>
+        <v>-0</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.08414199999999999</v>
+        <v>-0</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.084132</v>
+        <v>-0</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7356,42 +7380,42 @@
         <v/>
       </c>
       <c r="AC28" s="24" t="n">
-        <v>0.926762</v>
+        <v>0.926737</v>
       </c>
       <c r="AD28" s="24" t="n">
-        <v>0.926708</v>
+        <v>0.926739</v>
       </c>
       <c r="AE28" s="25">
         <f>IFERROR(subQ!AE16/subQ!AE15,"")</f>
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
-        <v>0.926756</v>
+        <v>0.92674</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.926763</v>
+        <v>0.926741</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.9267570000000001</v>
+        <v>0.926741</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.926747</v>
+        <v>0.926739</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.926739</v>
+        <v>0.92674</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.926756</v>
+        <v>0.926737</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.926698</v>
+        <v>0.926741</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.926767</v>
+        <v>0.926741</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -7637,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
@@ -7647,10 +7671,10 @@
         <v>216.02</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -7752,33 +7776,33 @@
         <v>-0.0034</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>216.03</v>
+        <v>216.02</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="29" t="n">
+        <v>216.02</v>
+      </c>
+      <c r="AM31" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="29" t="n">
         <v>-0</v>
-      </c>
-      <c r="AL31" s="29" t="n">
-        <v>216.03</v>
-      </c>
-      <c r="AM31" s="29" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AN31" s="29" t="n">
-        <v>0.01</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -7876,18 +7900,38 @@
         <f>IFERROR(subQ!AB21/subQ!AA21-1,"")</f>
         <v/>
       </c>
-      <c r="AC32" s="31" t="n"/>
-      <c r="AD32" s="31" t="n"/>
+      <c r="AC32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="AE32" s="25" t="n"/>
-      <c r="AF32" s="31" t="n"/>
-      <c r="AG32" s="31" t="n"/>
-      <c r="AH32" s="31" t="n"/>
-      <c r="AI32" s="31" t="n"/>
+      <c r="AF32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ32" s="25" t="n"/>
-      <c r="AK32" s="31" t="n"/>
-      <c r="AL32" s="31" t="n"/>
-      <c r="AM32" s="31" t="n"/>
-      <c r="AN32" s="31" t="n"/>
+      <c r="AK32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="AO32" s="25" t="n"/>
     </row>
     <row r="33">
@@ -7984,18 +8028,38 @@
         <f>IFERROR(subQ!AB22/subQ!AA22-1,"")</f>
         <v/>
       </c>
-      <c r="AC33" s="31" t="n"/>
-      <c r="AD33" s="31" t="n"/>
+      <c r="AC33" s="24" t="n">
+        <v>0.088196</v>
+      </c>
+      <c r="AD33" s="24" t="n">
+        <v>0.08251600000000001</v>
+      </c>
       <c r="AE33" s="25" t="n"/>
-      <c r="AF33" s="31" t="n"/>
-      <c r="AG33" s="31" t="n"/>
-      <c r="AH33" s="31" t="n"/>
-      <c r="AI33" s="31" t="n"/>
+      <c r="AF33" s="24" t="n">
+        <v>0.07684100000000001</v>
+      </c>
+      <c r="AG33" s="24" t="n">
+        <v>0.084165</v>
+      </c>
+      <c r="AH33" s="24" t="n">
+        <v>0.07095600000000001</v>
+      </c>
+      <c r="AI33" s="24" t="n">
+        <v>0.067465</v>
+      </c>
       <c r="AJ33" s="25" t="n"/>
-      <c r="AK33" s="31" t="n"/>
-      <c r="AL33" s="31" t="n"/>
-      <c r="AM33" s="31" t="n"/>
-      <c r="AN33" s="31" t="n"/>
+      <c r="AK33" s="24" t="n">
+        <v>0.063733</v>
+      </c>
+      <c r="AL33" s="24" t="n">
+        <v>0.06984899999999999</v>
+      </c>
+      <c r="AM33" s="24" t="n">
+        <v>0.060507</v>
+      </c>
+      <c r="AN33" s="24" t="n">
+        <v>0.058125</v>
+      </c>
       <c r="AO33" s="25" t="n"/>
     </row>
     <row r="34">
@@ -8093,36 +8157,36 @@
         <v/>
       </c>
       <c r="AC34" s="24" t="n">
-        <v>0.063689</v>
+        <v>-0.534289</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.070857</v>
+        <v>-1.168035</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.073855</v>
+        <v>7.007248</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.001374</v>
+        <v>1.032182</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.059336</v>
+        <v>0.464242</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.063232</v>
+        <v>0.322846</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.06458899999999999</v>
+        <v>0.246105</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.004054</v>
+        <v>0.230247</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.052112</v>
+        <v>0.173448</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.055101</v>
+        <v>0.150584</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8750,38 +8814,18 @@
         <f>IFERROR(subQ!AB31/subQ!W31-1,"")</f>
         <v/>
       </c>
-      <c r="AC40" s="24" t="n">
-        <v>-0.68242</v>
-      </c>
-      <c r="AD40" s="24" t="n">
-        <v>-0.323052</v>
-      </c>
+      <c r="AC40" s="31" t="n"/>
+      <c r="AD40" s="31" t="n"/>
       <c r="AE40" s="25" t="n"/>
-      <c r="AF40" s="24" t="n">
-        <v>-0.080092</v>
-      </c>
-      <c r="AG40" s="24" t="n">
-        <v>-0.496575</v>
-      </c>
-      <c r="AH40" s="24" t="n">
-        <v>-0.151786</v>
-      </c>
-      <c r="AI40" s="24" t="n">
-        <v>-0.330935</v>
-      </c>
+      <c r="AF40" s="31" t="n"/>
+      <c r="AG40" s="31" t="n"/>
+      <c r="AH40" s="31" t="n"/>
+      <c r="AI40" s="31" t="n"/>
       <c r="AJ40" s="25" t="n"/>
-      <c r="AK40" s="24" t="n">
-        <v>-0.31592</v>
-      </c>
-      <c r="AL40" s="24" t="n">
-        <v>-0.07823099999999999</v>
-      </c>
-      <c r="AM40" s="24" t="n">
-        <v>-0.059649</v>
-      </c>
-      <c r="AN40" s="24" t="n">
-        <v>-0.050179</v>
-      </c>
+      <c r="AK40" s="31" t="n"/>
+      <c r="AL40" s="31" t="n"/>
+      <c r="AM40" s="31" t="n"/>
+      <c r="AN40" s="31" t="n"/>
       <c r="AO40" s="25" t="n"/>
     </row>
     <row r="41">
@@ -8870,37 +8914,21 @@
         <v/>
       </c>
       <c r="AC41" s="24" t="n">
-        <v>-0.371681</v>
+        <v>0.221239</v>
       </c>
       <c r="AD41" s="24" t="n">
-        <v>-0.45082</v>
+        <v>6.688525</v>
       </c>
       <c r="AE41" s="25" t="n"/>
-      <c r="AF41" s="24" t="n">
-        <v>-0.432432</v>
-      </c>
-      <c r="AG41" s="24" t="n">
-        <v>-0.470588</v>
-      </c>
-      <c r="AH41" s="24" t="n">
-        <v>-0.15493</v>
-      </c>
-      <c r="AI41" s="24" t="n">
-        <v>-0.149254</v>
-      </c>
+      <c r="AF41" s="31" t="n"/>
+      <c r="AG41" s="31" t="n"/>
+      <c r="AH41" s="31" t="n"/>
+      <c r="AI41" s="31" t="n"/>
       <c r="AJ41" s="25" t="n"/>
-      <c r="AK41" s="24" t="n">
-        <v>-0.142857</v>
-      </c>
-      <c r="AL41" s="24" t="n">
-        <v>-0.142857</v>
-      </c>
-      <c r="AM41" s="24" t="n">
-        <v>-0.133333</v>
-      </c>
-      <c r="AN41" s="24" t="n">
-        <v>-0.140351</v>
-      </c>
+      <c r="AK41" s="31" t="n"/>
+      <c r="AL41" s="31" t="n"/>
+      <c r="AM41" s="31" t="n"/>
+      <c r="AN41" s="31" t="n"/>
       <c r="AO41" s="25" t="n"/>
     </row>
     <row r="42">
@@ -9171,42 +9199,42 @@
         <v/>
       </c>
       <c r="AC43" s="24" t="n">
-        <v>0.070673</v>
+        <v>0.070678</v>
       </c>
       <c r="AD43" s="24" t="n">
-        <v>0.070674</v>
+        <v>0.070677</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE34/subQ!AE33,"")</f>
         <v/>
       </c>
       <c r="AF43" s="24" t="n">
+        <v>0.070676</v>
+      </c>
+      <c r="AG43" s="24" t="n">
         <v>0.070674</v>
       </c>
-      <c r="AG43" s="24" t="n">
-        <v>0.070675</v>
-      </c>
       <c r="AH43" s="24" t="n">
-        <v>0.070675</v>
+        <v>0.070673</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>0.070675</v>
+        <v>0.070677</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ34/subQ!AJ33,"")</f>
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
+        <v>0.070675</v>
+      </c>
+      <c r="AL43" s="24" t="n">
+        <v>0.070674</v>
+      </c>
+      <c r="AM43" s="24" t="n">
         <v>0.070677</v>
       </c>
-      <c r="AL43" s="24" t="n">
-        <v>0.070673</v>
-      </c>
-      <c r="AM43" s="24" t="n">
-        <v>0.070673</v>
-      </c>
       <c r="AN43" s="24" t="n">
-        <v>0.070674</v>
+        <v>0.070675</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO34/subQ!AO33,"")</f>
@@ -9701,7 +9729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO98"/>
+  <dimension ref="A1:AO104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9949,7 +9977,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12471,8 +12499,15 @@
       <c r="X28" s="18" t="n">
         <v>99108.24000000001</v>
       </c>
-      <c r="Z28" s="9" t="n"/>
-      <c r="AB28" s="5" t="n"/>
+      <c r="Y28" s="18" t="n">
+        <v>100368.24</v>
+      </c>
+      <c r="Z28" s="34" t="n">
+        <v>100368.24</v>
+      </c>
+      <c r="AB28" s="19" t="n">
+        <v>96788.24000000001</v>
+      </c>
       <c r="AC28" s="10" t="n"/>
       <c r="AD28" s="10" t="n"/>
       <c r="AE28" s="11" t="n"/>
@@ -12985,8 +13020,15 @@
       <c r="X34" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n"/>
-      <c r="AB34" s="5" t="n"/>
+      <c r="Y34" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="AC34" s="10" t="n"/>
       <c r="AD34" s="10" t="n"/>
       <c r="AE34" s="11" t="n"/>
@@ -13062,8 +13104,15 @@
       <c r="X35" s="18" t="n">
         <v>68420</v>
       </c>
-      <c r="Z35" s="9" t="n"/>
-      <c r="AB35" s="5" t="n"/>
+      <c r="Y35" s="18" t="n">
+        <v>1463257.92</v>
+      </c>
+      <c r="Z35" s="34" t="n">
+        <v>1463257.92</v>
+      </c>
+      <c r="AB35" s="19" t="n">
+        <v>1755123.43</v>
+      </c>
       <c r="AC35" s="10" t="n"/>
       <c r="AD35" s="10" t="n"/>
       <c r="AE35" s="11" t="n"/>
@@ -13791,8 +13840,15 @@
       <c r="X44" s="18" t="n">
         <v>167528.24</v>
       </c>
-      <c r="Z44" s="9" t="n"/>
-      <c r="AB44" s="5" t="n"/>
+      <c r="Y44" s="18" t="n">
+        <v>1563626.16</v>
+      </c>
+      <c r="Z44" s="34" t="n">
+        <v>1563626.16</v>
+      </c>
+      <c r="AB44" s="19" t="n">
+        <v>1851911.67</v>
+      </c>
       <c r="AC44" s="10" t="n"/>
       <c r="AD44" s="10" t="n"/>
       <c r="AE44" s="11" t="n"/>
@@ -13868,8 +13924,15 @@
       <c r="X45" s="18" t="n">
         <v>156533.84</v>
       </c>
-      <c r="Z45" s="9" t="n"/>
-      <c r="AB45" s="5" t="n"/>
+      <c r="Y45" s="18" t="n">
+        <v>1410106.05</v>
+      </c>
+      <c r="Z45" s="34" t="n">
+        <v>1410106.05</v>
+      </c>
+      <c r="AB45" s="19" t="n">
+        <v>1719569.16</v>
+      </c>
       <c r="AC45" s="10" t="n"/>
       <c r="AD45" s="10" t="n"/>
       <c r="AE45" s="11" t="n"/>
@@ -16328,78 +16391,16 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>-166098.55</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="G78" s="18" t="n">
-        <v>198135.41</v>
-      </c>
-      <c r="H78" s="18" t="n">
-        <v>55928.38</v>
-      </c>
-      <c r="I78" s="18" t="n">
-        <v>-133337.45</v>
-      </c>
-      <c r="J78" s="18" t="n">
-        <v>-77396.07000000001</v>
-      </c>
-      <c r="K78" s="34" t="n">
-        <v>43330.27</v>
-      </c>
-      <c r="L78" s="18" t="n">
-        <v>-193282.65</v>
-      </c>
-      <c r="M78" s="18" t="n">
-        <v>173678.2</v>
-      </c>
-      <c r="N78" s="18" t="n">
-        <v>-52784.74</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>-187280.14</v>
-      </c>
-      <c r="P78" s="34" t="n">
-        <v>-259669.33</v>
-      </c>
-      <c r="Q78" s="18" t="n">
-        <v>-4525.59</v>
-      </c>
-      <c r="R78" s="18" t="n">
-        <v>26373.18</v>
-      </c>
-      <c r="S78" s="18" t="n">
-        <v>-480123.87</v>
-      </c>
-      <c r="T78" s="18" t="n">
-        <v>274152.1</v>
-      </c>
-      <c r="U78" s="34" t="n">
-        <v>-184124.18</v>
-      </c>
-      <c r="V78" s="18" t="n">
-        <v>-626.4400000000001</v>
-      </c>
-      <c r="W78" s="18" t="n">
-        <v>-75588.81</v>
-      </c>
-      <c r="X78" s="18" t="n">
-        <v>90242.34</v>
-      </c>
-      <c r="Y78" s="18" t="n">
-        <v>174407.1</v>
-      </c>
-      <c r="Z78" s="34" t="n">
-        <v>188434.19</v>
-      </c>
-      <c r="AA78" s="18" t="n">
-        <v>-382517.37</v>
-      </c>
+      <c r="K78" s="9" t="n"/>
+      <c r="P78" s="9" t="n"/>
+      <c r="U78" s="9" t="n"/>
+      <c r="Z78" s="9" t="n"/>
       <c r="AB78" s="19" t="n">
-        <v>51018.13</v>
+        <v>141.27</v>
       </c>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -16421,78 +16422,16 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>8158.88</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F79" s="9" t="n"/>
-      <c r="G79" s="18" t="n">
-        <v>9816.370000000001</v>
-      </c>
-      <c r="H79" s="18" t="n">
-        <v>13360.95</v>
-      </c>
-      <c r="I79" s="18" t="n">
-        <v>14125.87</v>
-      </c>
-      <c r="J79" s="18" t="n">
-        <v>17951.31</v>
-      </c>
-      <c r="K79" s="34" t="n">
-        <v>55254.5</v>
-      </c>
-      <c r="L79" s="18" t="n">
-        <v>17745.06</v>
-      </c>
-      <c r="M79" s="18" t="n">
-        <v>17482.98</v>
-      </c>
-      <c r="N79" s="18" t="n">
-        <v>14771.4</v>
-      </c>
-      <c r="O79" s="18" t="n">
-        <v>15914.83</v>
-      </c>
-      <c r="P79" s="34" t="n">
-        <v>65914.27</v>
-      </c>
-      <c r="Q79" s="18" t="n">
-        <v>19275.38</v>
-      </c>
-      <c r="R79" s="18" t="n">
-        <v>18342.85</v>
-      </c>
-      <c r="S79" s="18" t="n">
-        <v>20013.51</v>
-      </c>
-      <c r="T79" s="18" t="n">
-        <v>19434.24</v>
-      </c>
-      <c r="U79" s="34" t="n">
-        <v>77065.98</v>
-      </c>
-      <c r="V79" s="18" t="n">
-        <v>20665.83</v>
-      </c>
-      <c r="W79" s="18" t="n">
-        <v>19426.62</v>
-      </c>
-      <c r="X79" s="18" t="n">
-        <v>20092.3</v>
-      </c>
-      <c r="Y79" s="18" t="n">
-        <v>16301.07</v>
-      </c>
-      <c r="Z79" s="34" t="n">
-        <v>76485.82000000001</v>
-      </c>
-      <c r="AA79" s="18" t="n">
-        <v>18506.91</v>
-      </c>
+      <c r="K79" s="9" t="n"/>
+      <c r="P79" s="9" t="n"/>
+      <c r="U79" s="9" t="n"/>
+      <c r="Z79" s="9" t="n"/>
       <c r="AB79" s="19" t="n">
-        <v>22859.38</v>
+        <v>29</v>
       </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
@@ -16514,78 +16453,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>752.65</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="18" t="n">
-        <v>2175.22</v>
-      </c>
-      <c r="H80" s="18" t="n">
-        <v>3062.5</v>
-      </c>
-      <c r="I80" s="18" t="n">
-        <v>355.93</v>
-      </c>
-      <c r="J80" s="18" t="n">
-        <v>631.78</v>
-      </c>
-      <c r="K80" s="34" t="n">
-        <v>6225.43</v>
-      </c>
-      <c r="L80" s="18" t="n">
-        <v>335.67</v>
-      </c>
-      <c r="M80" s="18" t="n">
-        <v>2646.86</v>
-      </c>
-      <c r="N80" s="18" t="n">
-        <v>3690.29</v>
-      </c>
-      <c r="O80" s="18" t="n">
-        <v>2994.7</v>
-      </c>
-      <c r="P80" s="34" t="n">
-        <v>9667.52</v>
-      </c>
-      <c r="Q80" s="18" t="n">
-        <v>443.54</v>
-      </c>
-      <c r="R80" s="18" t="n">
-        <v>5488.88</v>
-      </c>
-      <c r="S80" s="18" t="n">
-        <v>713.71</v>
-      </c>
-      <c r="T80" s="18" t="n">
-        <v>2158.83</v>
-      </c>
-      <c r="U80" s="34" t="n">
-        <v>8804.959999999999</v>
-      </c>
-      <c r="V80" s="18" t="n">
-        <v>1408.57</v>
-      </c>
-      <c r="W80" s="18" t="n">
-        <v>4246.54</v>
-      </c>
-      <c r="X80" s="18" t="n">
-        <v>765.41</v>
-      </c>
-      <c r="Y80" s="18" t="n">
-        <v>1452.82</v>
-      </c>
-      <c r="Z80" s="34" t="n">
-        <v>7873.34</v>
-      </c>
-      <c r="AA80" s="18" t="n">
-        <v>2124.15</v>
-      </c>
+      <c r="K80" s="9" t="n"/>
+      <c r="P80" s="9" t="n"/>
+      <c r="U80" s="9" t="n"/>
+      <c r="Z80" s="9" t="n"/>
       <c r="AB80" s="19" t="n">
-        <v>6352.84</v>
+        <v>1938.35</v>
       </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
@@ -16607,61 +16484,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>-5084.28</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="18" t="n">
-        <v>-6300.3</v>
-      </c>
-      <c r="H81" s="18" t="n">
-        <v>-7202.54</v>
-      </c>
-      <c r="I81" s="18" t="n">
-        <v>-9592.52</v>
-      </c>
-      <c r="J81" s="18" t="n">
-        <v>-13011.37</v>
-      </c>
-      <c r="K81" s="34" t="n">
-        <v>-36106.73</v>
-      </c>
-      <c r="L81" s="18" t="n">
-        <v>-15072.34</v>
-      </c>
-      <c r="M81" s="18" t="n">
-        <v>-16572.4</v>
-      </c>
+      <c r="K81" s="9" t="n"/>
       <c r="P81" s="9" t="n"/>
-      <c r="Q81" s="18" t="n">
-        <v>-16056.01</v>
-      </c>
-      <c r="R81" s="18" t="n">
-        <v>-15854.54</v>
-      </c>
-      <c r="S81" s="18" t="n">
-        <v>-19594.9</v>
-      </c>
-      <c r="T81" s="18" t="n">
-        <v>-18324.91</v>
-      </c>
-      <c r="U81" s="34" t="n">
-        <v>-69830.36</v>
-      </c>
-      <c r="V81" s="18" t="n">
-        <v>-17524.42</v>
-      </c>
-      <c r="W81" s="18" t="n">
-        <v>-16246.29</v>
-      </c>
-      <c r="X81" s="18" t="n">
-        <v>-14506.26</v>
-      </c>
+      <c r="U81" s="9" t="n"/>
       <c r="Z81" s="9" t="n"/>
-      <c r="AB81" s="5" t="n"/>
+      <c r="AB81" s="19" t="n">
+        <v>138.95</v>
+      </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
       <c r="AE81" s="11" t="n"/>
@@ -16682,78 +16515,16 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>-851.91</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="G82" s="18" t="n">
-        <v>-4501.99</v>
-      </c>
-      <c r="H82" s="18" t="n">
-        <v>-5745.98</v>
-      </c>
-      <c r="I82" s="18" t="n">
-        <v>-3004.08</v>
-      </c>
-      <c r="J82" s="18" t="n">
-        <v>-2236.08</v>
-      </c>
-      <c r="K82" s="34" t="n">
-        <v>-15488.13</v>
-      </c>
-      <c r="L82" s="18" t="n">
-        <v>-2811.64</v>
-      </c>
-      <c r="M82" s="18" t="n">
-        <v>445.09</v>
-      </c>
-      <c r="N82" s="18" t="n">
-        <v>-2166.84</v>
-      </c>
-      <c r="O82" s="18" t="n">
-        <v>-2472.79</v>
-      </c>
-      <c r="P82" s="34" t="n">
-        <v>-7006.18</v>
-      </c>
-      <c r="Q82" s="18" t="n">
-        <v>-2480.67</v>
-      </c>
-      <c r="R82" s="18" t="n">
-        <v>-2304.49</v>
-      </c>
-      <c r="S82" s="18" t="n">
-        <v>-3317.93</v>
-      </c>
-      <c r="T82" s="18" t="n">
-        <v>-8105.81</v>
-      </c>
-      <c r="U82" s="34" t="n">
-        <v>-16208.9</v>
-      </c>
-      <c r="V82" s="18" t="n">
-        <v>-2691.75</v>
-      </c>
-      <c r="W82" s="18" t="n">
-        <v>2220.97</v>
-      </c>
-      <c r="X82" s="18" t="n">
-        <v>-2234.28</v>
-      </c>
-      <c r="Y82" s="18" t="n">
-        <v>-673.66</v>
-      </c>
-      <c r="Z82" s="34" t="n">
-        <v>-3378.72</v>
-      </c>
-      <c r="AA82" s="18" t="n">
-        <v>-2109.77</v>
-      </c>
+      <c r="K82" s="9" t="n"/>
+      <c r="P82" s="9" t="n"/>
+      <c r="U82" s="9" t="n"/>
+      <c r="Z82" s="9" t="n"/>
       <c r="AB82" s="19" t="n">
-        <v>2804.35</v>
+        <v>8.01</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -16775,78 +16546,16 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>4834.08</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F83" s="9" t="n"/>
-      <c r="G83" s="18" t="n">
-        <v>4446.47</v>
-      </c>
-      <c r="H83" s="18" t="n">
-        <v>-2857.71</v>
-      </c>
-      <c r="I83" s="18" t="n">
-        <v>-591.67</v>
-      </c>
-      <c r="J83" s="18" t="n">
-        <v>4385.15</v>
-      </c>
-      <c r="K83" s="34" t="n">
-        <v>5382.24</v>
-      </c>
-      <c r="L83" s="18" t="n">
-        <v>-2478.46</v>
-      </c>
-      <c r="M83" s="18" t="n">
-        <v>-14815.85</v>
-      </c>
-      <c r="N83" s="18" t="n">
-        <v>4104.52</v>
-      </c>
-      <c r="O83" s="18" t="n">
-        <v>22009.22</v>
-      </c>
-      <c r="P83" s="34" t="n">
-        <v>8819.43</v>
-      </c>
-      <c r="Q83" s="18" t="n">
-        <v>9175.620000000001</v>
-      </c>
-      <c r="R83" s="18" t="n">
-        <v>6612.97</v>
-      </c>
-      <c r="S83" s="18" t="n">
-        <v>-6729.9</v>
-      </c>
-      <c r="T83" s="18" t="n">
-        <v>7167.09</v>
-      </c>
-      <c r="U83" s="34" t="n">
-        <v>16225.78</v>
-      </c>
-      <c r="V83" s="18" t="n">
-        <v>1310.85</v>
-      </c>
-      <c r="W83" s="18" t="n">
-        <v>4330.78</v>
-      </c>
-      <c r="X83" s="18" t="n">
-        <v>-2477.52</v>
-      </c>
-      <c r="Y83" s="18" t="n">
-        <v>10055.34</v>
-      </c>
-      <c r="Z83" s="34" t="n">
-        <v>13219.45</v>
-      </c>
-      <c r="AA83" s="18" t="n">
-        <v>-9421.07</v>
-      </c>
+      <c r="K83" s="9" t="n"/>
+      <c r="P83" s="9" t="n"/>
+      <c r="U83" s="9" t="n"/>
+      <c r="Z83" s="9" t="n"/>
       <c r="AB83" s="19" t="n">
-        <v>4510.06</v>
+        <v>-1797.08</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -16868,69 +16577,79 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E84" s="18" t="n">
-        <v>55.56</v>
+        <v>-166098.55</v>
       </c>
       <c r="F84" s="9" t="n"/>
       <c r="G84" s="18" t="n">
-        <v>165.32</v>
+        <v>198135.41</v>
       </c>
       <c r="H84" s="18" t="n">
-        <v>331.85</v>
+        <v>55928.38</v>
       </c>
       <c r="I84" s="18" t="n">
-        <v>16.67</v>
+        <v>-133337.45</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>242.1</v>
+        <v>-77396.07000000001</v>
       </c>
       <c r="K84" s="34" t="n">
-        <v>755.9400000000001</v>
+        <v>43330.27</v>
       </c>
       <c r="L84" s="18" t="n">
-        <v>436.15</v>
+        <v>-193282.65</v>
       </c>
       <c r="M84" s="18" t="n">
-        <v>0</v>
+        <v>173678.2</v>
       </c>
       <c r="N84" s="18" t="n">
-        <v>190.8</v>
+        <v>-52784.74</v>
       </c>
       <c r="O84" s="18" t="n">
-        <v>32.7</v>
+        <v>-187280.14</v>
       </c>
       <c r="P84" s="34" t="n">
-        <v>659.65</v>
+        <v>-259669.33</v>
       </c>
       <c r="Q84" s="18" t="n">
-        <v>7.48</v>
+        <v>-4525.59</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.03</v>
+        <v>26373.18</v>
       </c>
       <c r="S84" s="18" t="n">
-        <v>804.7</v>
+        <v>-480123.87</v>
       </c>
       <c r="T84" s="18" t="n">
-        <v>17.19</v>
+        <v>274152.1</v>
       </c>
       <c r="U84" s="34" t="n">
-        <v>829.4</v>
+        <v>-184124.18</v>
       </c>
       <c r="V84" s="18" t="n">
-        <v>2458.97</v>
+        <v>-626.4400000000001</v>
       </c>
       <c r="W84" s="18" t="n">
-        <v>96.95999999999999</v>
+        <v>-75588.81</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z84" s="9" t="n"/>
-      <c r="AB84" s="5" t="n"/>
+        <v>90242.34</v>
+      </c>
+      <c r="Y84" s="18" t="n">
+        <v>174407.1</v>
+      </c>
+      <c r="Z84" s="34" t="n">
+        <v>188434.19</v>
+      </c>
+      <c r="AA84" s="18" t="n">
+        <v>-382517.37</v>
+      </c>
+      <c r="AB84" s="19" t="n">
+        <v>51018.13</v>
+      </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
       <c r="AE84" s="11" t="n"/>
@@ -16951,78 +16670,78 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E85" s="18" t="n">
-        <v>55.56</v>
+        <v>8158.88</v>
       </c>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="18" t="n">
-        <v>165.32</v>
+        <v>9816.370000000001</v>
       </c>
       <c r="H85" s="18" t="n">
-        <v>331.85</v>
+        <v>13360.95</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>16.67</v>
+        <v>14125.87</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>242.1</v>
+        <v>17951.31</v>
       </c>
       <c r="K85" s="34" t="n">
-        <v>755.9400000000001</v>
+        <v>55254.5</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>436.15</v>
+        <v>17745.06</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>1701.81</v>
+        <v>17482.98</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>360.95</v>
+        <v>14771.4</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>147.08</v>
+        <v>15914.83</v>
       </c>
       <c r="P85" s="34" t="n">
-        <v>2645.99</v>
+        <v>65914.27</v>
       </c>
       <c r="Q85" s="18" t="n">
-        <v>88.68000000000001</v>
+        <v>19275.38</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>61.73</v>
+        <v>18342.85</v>
       </c>
       <c r="S85" s="18" t="n">
-        <v>885.8200000000001</v>
+        <v>20013.51</v>
       </c>
       <c r="T85" s="18" t="n">
-        <v>40.35</v>
+        <v>19434.24</v>
       </c>
       <c r="U85" s="34" t="n">
-        <v>1076.58</v>
+        <v>77065.98</v>
       </c>
       <c r="V85" s="18" t="n">
-        <v>2520.59</v>
+        <v>20665.83</v>
       </c>
       <c r="W85" s="18" t="n">
-        <v>216.91</v>
+        <v>19426.62</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>167.69</v>
+        <v>20092.3</v>
       </c>
       <c r="Y85" s="18" t="n">
-        <v>672.09</v>
+        <v>16301.07</v>
       </c>
       <c r="Z85" s="34" t="n">
-        <v>3577.28</v>
+        <v>76485.82000000001</v>
       </c>
       <c r="AA85" s="18" t="n">
-        <v>110.31</v>
+        <v>18506.91</v>
       </c>
       <c r="AB85" s="19" t="n">
-        <v>547.4400000000001</v>
+        <v>22859.38</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -17044,78 +16763,78 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>124247.45</v>
+        <v>752.65</v>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="G86" s="18" t="n">
-        <v>-157873.66</v>
+        <v>2175.22</v>
       </c>
       <c r="H86" s="18" t="n">
-        <v>-44360.14</v>
+        <v>3062.5</v>
       </c>
       <c r="I86" s="18" t="n">
-        <v>105092.08</v>
+        <v>355.93</v>
       </c>
       <c r="J86" s="18" t="n">
-        <v>71491.64999999999</v>
+        <v>631.78</v>
       </c>
       <c r="K86" s="34" t="n">
-        <v>-25650.07</v>
+        <v>6225.43</v>
       </c>
       <c r="L86" s="18" t="n">
-        <v>214647.23</v>
+        <v>335.67</v>
       </c>
       <c r="M86" s="18" t="n">
-        <v>-128188.34</v>
+        <v>2646.86</v>
       </c>
       <c r="N86" s="18" t="n">
-        <v>4559.06</v>
+        <v>3690.29</v>
       </c>
       <c r="O86" s="18" t="n">
-        <v>158408.39</v>
+        <v>2994.7</v>
       </c>
       <c r="P86" s="34" t="n">
-        <v>249426.34</v>
+        <v>9667.52</v>
       </c>
       <c r="Q86" s="18" t="n">
-        <v>10338.19</v>
+        <v>443.54</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>-17263.59</v>
+        <v>5488.88</v>
       </c>
       <c r="S86" s="18" t="n">
-        <v>462970.53</v>
+        <v>713.71</v>
       </c>
       <c r="T86" s="18" t="n">
-        <v>-274877.8</v>
+        <v>2158.83</v>
       </c>
       <c r="U86" s="34" t="n">
-        <v>181167.33</v>
+        <v>8804.959999999999</v>
       </c>
       <c r="V86" s="18" t="n">
-        <v>23065.7</v>
+        <v>1408.57</v>
       </c>
       <c r="W86" s="18" t="n">
-        <v>70197.48</v>
+        <v>4246.54</v>
       </c>
       <c r="X86" s="18" t="n">
-        <v>-102263.05</v>
+        <v>765.41</v>
       </c>
       <c r="Y86" s="18" t="n">
-        <v>-152875.34</v>
+        <v>1452.82</v>
       </c>
       <c r="Z86" s="34" t="n">
-        <v>-161875.21</v>
+        <v>7873.34</v>
       </c>
       <c r="AA86" s="18" t="n">
-        <v>360592.09</v>
+        <v>2124.15</v>
       </c>
       <c r="AB86" s="19" t="n">
-        <v>-45359.44</v>
+        <v>6352.84</v>
       </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
@@ -17137,53 +16856,61 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E87" s="18" t="n">
-        <v>6000</v>
+        <v>-5084.28</v>
       </c>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="18" t="n">
-        <v>95000</v>
+        <v>-6300.3</v>
       </c>
       <c r="H87" s="18" t="n">
-        <v>62.59</v>
+        <v>-7202.54</v>
+      </c>
+      <c r="I87" s="18" t="n">
+        <v>-9592.52</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>2970</v>
-      </c>
-      <c r="K87" s="9" t="n"/>
+        <v>-13011.37</v>
+      </c>
+      <c r="K87" s="34" t="n">
+        <v>-36106.73</v>
+      </c>
       <c r="L87" s="18" t="n">
-        <v>6420</v>
+        <v>-15072.34</v>
       </c>
       <c r="M87" s="18" t="n">
-        <v>1760</v>
-      </c>
-      <c r="N87" s="18" t="n">
-        <v>8320</v>
+        <v>-16572.4</v>
       </c>
       <c r="P87" s="9" t="n"/>
       <c r="Q87" s="18" t="n">
-        <v>16400</v>
+        <v>-16056.01</v>
+      </c>
+      <c r="R87" s="18" t="n">
+        <v>-15854.54</v>
       </c>
       <c r="S87" s="18" t="n">
-        <v>13000</v>
-      </c>
-      <c r="U87" s="9" t="n"/>
+        <v>-19594.9</v>
+      </c>
+      <c r="T87" s="18" t="n">
+        <v>-18324.91</v>
+      </c>
+      <c r="U87" s="34" t="n">
+        <v>-69830.36</v>
+      </c>
       <c r="V87" s="18" t="n">
-        <v>93410</v>
+        <v>-17524.42</v>
+      </c>
+      <c r="W87" s="18" t="n">
+        <v>-16246.29</v>
       </c>
       <c r="X87" s="18" t="n">
-        <v>6260</v>
+        <v>-14506.26</v>
       </c>
       <c r="Z87" s="9" t="n"/>
-      <c r="AA87" s="18" t="n">
-        <v>1380</v>
-      </c>
-      <c r="AB87" s="19" t="n">
-        <v>990</v>
-      </c>
+      <c r="AB87" s="5" t="n"/>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
       <c r="AE87" s="11" t="n"/>
@@ -17204,78 +16931,78 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E88" s="18" t="n">
-        <v>0</v>
+        <v>-851.91</v>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="18" t="n">
-        <v>17000</v>
+        <v>-4501.99</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>0</v>
+        <v>-5745.98</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>0</v>
+        <v>-3004.08</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>0</v>
+        <v>-2236.08</v>
       </c>
       <c r="K88" s="34" t="n">
-        <v>17000</v>
+        <v>-15488.13</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>20000</v>
+        <v>-2811.64</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>42000</v>
+        <v>445.09</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>0</v>
+        <v>-2166.84</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>0</v>
+        <v>-2472.79</v>
       </c>
       <c r="P88" s="34" t="n">
-        <v>62000</v>
+        <v>-7006.18</v>
       </c>
       <c r="Q88" s="18" t="n">
-        <v>0</v>
+        <v>-2480.67</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>40000</v>
+        <v>-2304.49</v>
       </c>
       <c r="S88" s="18" t="n">
-        <v>9000</v>
+        <v>-3317.93</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>18420</v>
+        <v>-8105.81</v>
       </c>
       <c r="U88" s="34" t="n">
-        <v>67420</v>
+        <v>-16208.9</v>
       </c>
       <c r="V88" s="18" t="n">
-        <v>16500</v>
+        <v>-2691.75</v>
       </c>
       <c r="W88" s="18" t="n">
-        <v>25000</v>
+        <v>2220.97</v>
       </c>
       <c r="X88" s="18" t="n">
-        <v>200</v>
+        <v>-2234.28</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>27340</v>
+        <v>-673.66</v>
       </c>
       <c r="Z88" s="34" t="n">
-        <v>69040</v>
+        <v>-3378.72</v>
       </c>
       <c r="AA88" s="18" t="n">
-        <v>12000</v>
+        <v>-2109.77</v>
       </c>
       <c r="AB88" s="19" t="n">
-        <v>19500</v>
+        <v>2804.35</v>
       </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
@@ -17297,43 +17024,78 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0</v>
+        <v>4834.08</v>
       </c>
       <c r="F89" s="9" t="n"/>
+      <c r="G89" s="18" t="n">
+        <v>4446.47</v>
+      </c>
+      <c r="H89" s="18" t="n">
+        <v>-2857.71</v>
+      </c>
+      <c r="I89" s="18" t="n">
+        <v>-591.67</v>
+      </c>
       <c r="J89" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="9" t="n"/>
+        <v>4385.15</v>
+      </c>
+      <c r="K89" s="34" t="n">
+        <v>5382.24</v>
+      </c>
+      <c r="L89" s="18" t="n">
+        <v>-2478.46</v>
+      </c>
+      <c r="M89" s="18" t="n">
+        <v>-14815.85</v>
+      </c>
+      <c r="N89" s="18" t="n">
+        <v>4104.52</v>
+      </c>
       <c r="O89" s="18" t="n">
-        <v>5000</v>
-      </c>
-      <c r="P89" s="9" t="n"/>
+        <v>22009.22</v>
+      </c>
+      <c r="P89" s="34" t="n">
+        <v>8819.43</v>
+      </c>
       <c r="Q89" s="18" t="n">
-        <v>15000</v>
+        <v>9175.620000000001</v>
+      </c>
+      <c r="R89" s="18" t="n">
+        <v>6612.97</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>0</v>
+        <v>-6729.9</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>29374.91</v>
-      </c>
-      <c r="U89" s="9" t="n"/>
+        <v>7167.09</v>
+      </c>
+      <c r="U89" s="34" t="n">
+        <v>16225.78</v>
+      </c>
       <c r="V89" s="18" t="n">
-        <v>90637.42999999999</v>
+        <v>1310.85</v>
+      </c>
+      <c r="W89" s="18" t="n">
+        <v>4330.78</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>5000</v>
-      </c>
-      <c r="Z89" s="9" t="n"/>
+        <v>-2477.52</v>
+      </c>
+      <c r="Y89" s="18" t="n">
+        <v>10055.34</v>
+      </c>
+      <c r="Z89" s="34" t="n">
+        <v>13219.45</v>
+      </c>
       <c r="AA89" s="18" t="n">
-        <v>1000</v>
+        <v>-9421.07</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>25800</v>
+        <v>4510.06</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -17355,71 +17117,68 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="E90" s="18" t="n">
-        <v>0</v>
+        <v>55.56</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>24000</v>
+        <v>165.32</v>
       </c>
       <c r="H90" s="18" t="n">
+        <v>331.85</v>
+      </c>
+      <c r="I90" s="18" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="J90" s="18" t="n">
+        <v>242.1</v>
+      </c>
+      <c r="K90" s="34" t="n">
+        <v>755.9400000000001</v>
+      </c>
+      <c r="L90" s="18" t="n">
+        <v>436.15</v>
+      </c>
+      <c r="M90" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="I90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="34" t="n">
-        <v>24000</v>
-      </c>
-      <c r="L90" s="18" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M90" s="18" t="n">
-        <v>30000</v>
-      </c>
       <c r="N90" s="18" t="n">
-        <v>0</v>
+        <v>190.8</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>0</v>
+        <v>32.7</v>
       </c>
       <c r="P90" s="34" t="n">
-        <v>50000</v>
+        <v>659.65</v>
       </c>
       <c r="Q90" s="18" t="n">
-        <v>0</v>
+        <v>7.48</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>42000</v>
+        <v>0.03</v>
       </c>
       <c r="S90" s="18" t="n">
-        <v>11000</v>
-      </c>
-      <c r="U90" s="9" t="n"/>
+        <v>804.7</v>
+      </c>
+      <c r="T90" s="18" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="U90" s="34" t="n">
+        <v>829.4</v>
+      </c>
       <c r="V90" s="18" t="n">
-        <v>12900</v>
+        <v>2458.97</v>
       </c>
       <c r="W90" s="18" t="n">
-        <v>22500</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>7000</v>
-      </c>
-      <c r="Y90" s="18" t="n">
-        <v>2420</v>
-      </c>
-      <c r="Z90" s="34" t="n">
-        <v>44820</v>
-      </c>
-      <c r="AA90" s="18" t="n">
-        <v>11000</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Z90" s="9" t="n"/>
       <c r="AB90" s="5" t="n"/>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -17441,77 +17200,79 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E91" s="18" t="n">
-        <v>82.27</v>
+        <v>55.56</v>
       </c>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="18" t="n">
-        <v>215.5</v>
+        <v>165.32</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>433.16</v>
+        <v>331.85</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>436.87</v>
+        <v>16.67</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>409.98</v>
+        <v>242.1</v>
       </c>
       <c r="K91" s="34" t="n">
-        <v>1495.51</v>
+        <v>755.9400000000001</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>486.9</v>
+        <v>436.15</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>596.37</v>
+        <v>1701.81</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>599.65</v>
+        <v>360.95</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>571.97</v>
+        <v>147.08</v>
       </c>
       <c r="P91" s="34" t="n">
-        <v>2254.89</v>
+        <v>2645.99</v>
       </c>
       <c r="Q91" s="18" t="n">
-        <v>650.8200000000001</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>772.2</v>
+        <v>61.73</v>
       </c>
       <c r="S91" s="18" t="n">
-        <v>772.02</v>
+        <v>885.8200000000001</v>
       </c>
       <c r="T91" s="18" t="n">
-        <v>743.35</v>
+        <v>40.35</v>
       </c>
       <c r="U91" s="34" t="n">
-        <v>2938.39</v>
+        <v>1076.58</v>
       </c>
       <c r="V91" s="18" t="n">
-        <v>776.3099999999999</v>
+        <v>2520.59</v>
       </c>
       <c r="W91" s="18" t="n">
-        <v>788.46</v>
+        <v>216.91</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>817.3</v>
+        <v>167.69</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>779.91</v>
+        <v>672.09</v>
       </c>
       <c r="Z91" s="34" t="n">
-        <v>3161.98</v>
+        <v>3577.28</v>
       </c>
       <c r="AA91" s="18" t="n">
-        <v>1653.2</v>
-      </c>
-      <c r="AB91" s="5" t="n"/>
+        <v>110.31</v>
+      </c>
+      <c r="AB91" s="19" t="n">
+        <v>547.4400000000001</v>
+      </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
       <c r="AE91" s="11" t="n"/>
@@ -17532,78 +17293,78 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E92" s="18" t="n">
-        <v>-74046.17</v>
+        <v>124247.45</v>
       </c>
       <c r="F92" s="9" t="n"/>
       <c r="G92" s="18" t="n">
-        <v>89416.61</v>
+        <v>-157873.66</v>
       </c>
       <c r="H92" s="18" t="n">
-        <v>17420.87</v>
+        <v>-44360.14</v>
       </c>
       <c r="I92" s="18" t="n">
-        <v>-57674.06</v>
+        <v>105092.08</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>-3097.89</v>
+        <v>71491.64999999999</v>
       </c>
       <c r="K92" s="34" t="n">
-        <v>46065.53</v>
+        <v>-25650.07</v>
       </c>
       <c r="L92" s="18" t="n">
-        <v>37772.24</v>
+        <v>214647.23</v>
       </c>
       <c r="M92" s="18" t="n">
-        <v>61348.02</v>
+        <v>-128188.34</v>
       </c>
       <c r="N92" s="18" t="n">
-        <v>-88242.32000000001</v>
+        <v>4559.06</v>
       </c>
       <c r="O92" s="18" t="n">
-        <v>-13725.06</v>
+        <v>158408.39</v>
       </c>
       <c r="P92" s="34" t="n">
-        <v>-2847.12</v>
+        <v>249426.34</v>
       </c>
       <c r="Q92" s="18" t="n">
-        <v>29976.44</v>
+        <v>10338.19</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>31445.1</v>
+        <v>-17263.59</v>
       </c>
       <c r="S92" s="18" t="n">
-        <v>-47766.46</v>
+        <v>462970.53</v>
       </c>
       <c r="T92" s="18" t="n">
-        <v>12882.78</v>
+        <v>-274877.8</v>
       </c>
       <c r="U92" s="34" t="n">
-        <v>26537.86</v>
+        <v>181167.33</v>
       </c>
       <c r="V92" s="18" t="n">
-        <v>47500.22</v>
+        <v>23065.7</v>
       </c>
       <c r="W92" s="18" t="n">
-        <v>-2121.1</v>
+        <v>70197.48</v>
       </c>
       <c r="X92" s="18" t="n">
-        <v>-28996.46</v>
+        <v>-102263.05</v>
       </c>
       <c r="Y92" s="18" t="n">
-        <v>23395.77</v>
+        <v>-152875.34</v>
       </c>
       <c r="Z92" s="34" t="n">
-        <v>39778.43</v>
+        <v>-161875.21</v>
       </c>
       <c r="AA92" s="18" t="n">
-        <v>-31346.36</v>
+        <v>360592.09</v>
       </c>
       <c r="AB92" s="19" t="n">
-        <v>10168.76</v>
+        <v>-45359.44</v>
       </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
@@ -17625,78 +17386,52 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>장기차입금의증가</t>
         </is>
       </c>
       <c r="E93" s="18" t="n">
-        <v>-37029.15</v>
+        <v>6000</v>
       </c>
       <c r="F93" s="9" t="n"/>
       <c r="G93" s="18" t="n">
-        <v>123601.61</v>
+        <v>95000</v>
       </c>
       <c r="H93" s="18" t="n">
-        <v>8710.360000000001</v>
-      </c>
-      <c r="I93" s="18" t="n">
-        <v>-28837.04</v>
+        <v>62.59</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>-1578.62</v>
-      </c>
-      <c r="K93" s="34" t="n">
-        <v>101896.31</v>
-      </c>
+        <v>2970</v>
+      </c>
+      <c r="K93" s="9" t="n"/>
       <c r="L93" s="18" t="n">
-        <v>120782.43</v>
+        <v>6420</v>
       </c>
       <c r="M93" s="18" t="n">
-        <v>30674.01</v>
+        <v>1760</v>
       </c>
       <c r="N93" s="18" t="n">
-        <v>-44121.16</v>
-      </c>
-      <c r="O93" s="18" t="n">
-        <v>-6862.53</v>
-      </c>
-      <c r="P93" s="34" t="n">
-        <v>100472.75</v>
-      </c>
+        <v>8320</v>
+      </c>
+      <c r="P93" s="9" t="n"/>
       <c r="Q93" s="18" t="n">
-        <v>115460.97</v>
-      </c>
-      <c r="R93" s="18" t="n">
-        <v>15722.55</v>
+        <v>16400</v>
       </c>
       <c r="S93" s="18" t="n">
-        <v>-23883.23</v>
-      </c>
-      <c r="T93" s="18" t="n">
-        <v>6441.39</v>
-      </c>
-      <c r="U93" s="34" t="n">
-        <v>113741.68</v>
-      </c>
+        <v>13000</v>
+      </c>
+      <c r="U93" s="9" t="n"/>
       <c r="V93" s="18" t="n">
-        <v>137491.8</v>
-      </c>
-      <c r="W93" s="18" t="n">
-        <v>-629.89</v>
+        <v>93410</v>
       </c>
       <c r="X93" s="18" t="n">
-        <v>-14498.23</v>
-      </c>
-      <c r="Y93" s="18" t="n">
-        <v>31156.43</v>
-      </c>
-      <c r="Z93" s="34" t="n">
-        <v>153520.11</v>
-      </c>
+        <v>6260</v>
+      </c>
+      <c r="Z93" s="9" t="n"/>
       <c r="AA93" s="18" t="n">
-        <v>122173.76</v>
+        <v>1380</v>
       </c>
       <c r="AB93" s="19" t="n">
-        <v>10168.75</v>
+        <v>990</v>
       </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
@@ -17718,36 +17453,79 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
-        </is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="9" t="n"/>
+      <c r="G94" s="18" t="n">
+        <v>17000</v>
+      </c>
+      <c r="H94" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="J94" s="18" t="n">
-        <v>3219.58</v>
-      </c>
-      <c r="K94" s="9" t="n"/>
-      <c r="P94" s="9" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="K94" s="34" t="n">
+        <v>17000</v>
+      </c>
+      <c r="L94" s="18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M94" s="18" t="n">
+        <v>42000</v>
+      </c>
+      <c r="N94" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="34" t="n">
+        <v>62000</v>
+      </c>
       <c r="Q94" s="18" t="n">
-        <v>1274.12</v>
+        <v>0</v>
+      </c>
+      <c r="R94" s="18" t="n">
+        <v>40000</v>
       </c>
       <c r="S94" s="18" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T94" s="18" t="n">
-        <v>1610.69</v>
-      </c>
-      <c r="U94" s="9" t="n"/>
+        <v>18420</v>
+      </c>
+      <c r="U94" s="34" t="n">
+        <v>67420</v>
+      </c>
       <c r="V94" s="18" t="n">
-        <v>0</v>
+        <v>16500</v>
       </c>
       <c r="W94" s="18" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="X94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="9" t="n"/>
-      <c r="AB94" s="5" t="n"/>
+        <v>200</v>
+      </c>
+      <c r="Y94" s="18" t="n">
+        <v>27340</v>
+      </c>
+      <c r="Z94" s="34" t="n">
+        <v>69040</v>
+      </c>
+      <c r="AA94" s="18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AB94" s="19" t="n">
+        <v>19500</v>
+      </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
       <c r="AE94" s="11" t="n"/>
@@ -17768,27 +17546,44 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
-        </is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="9" t="n"/>
+      <c r="J95" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="K95" s="9" t="n"/>
-      <c r="L95" s="18" t="n">
+      <c r="O95" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="N95" s="18" t="n">
-        <v>5000</v>
-      </c>
       <c r="P95" s="9" t="n"/>
+      <c r="Q95" s="18" t="n">
+        <v>15000</v>
+      </c>
       <c r="S95" s="18" t="n">
         <v>0</v>
       </c>
+      <c r="T95" s="18" t="n">
+        <v>29374.91</v>
+      </c>
       <c r="U95" s="9" t="n"/>
+      <c r="V95" s="18" t="n">
+        <v>90637.42999999999</v>
+      </c>
       <c r="X95" s="18" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Z95" s="9" t="n"/>
-      <c r="AB95" s="5" t="n"/>
+      <c r="AA95" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB95" s="19" t="n">
+        <v>25800</v>
+      </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
       <c r="AE95" s="11" t="n"/>
@@ -17809,43 +17604,71 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="9" t="n"/>
-      <c r="K96" s="9" t="n"/>
+      <c r="G96" s="18" t="n">
+        <v>24000</v>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="34" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L96" s="18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M96" s="18" t="n">
+        <v>30000</v>
+      </c>
       <c r="N96" s="18" t="n">
         <v>0</v>
       </c>
       <c r="O96" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="P96" s="9" t="n"/>
+      <c r="P96" s="34" t="n">
+        <v>50000</v>
+      </c>
       <c r="Q96" s="18" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="S96" s="18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" s="34" t="n">
-        <v>2</v>
-      </c>
+        <v>11000</v>
+      </c>
+      <c r="U96" s="9" t="n"/>
       <c r="V96" s="18" t="n">
-        <v>0</v>
+        <v>12900</v>
       </c>
       <c r="W96" s="18" t="n">
-        <v>0</v>
+        <v>22500</v>
       </c>
       <c r="X96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="9" t="n"/>
+        <v>7000</v>
+      </c>
+      <c r="Y96" s="18" t="n">
+        <v>2420</v>
+      </c>
+      <c r="Z96" s="34" t="n">
+        <v>44820</v>
+      </c>
+      <c r="AA96" s="18" t="n">
+        <v>11000</v>
+      </c>
       <c r="AB96" s="5" t="n"/>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
@@ -17867,54 +17690,77 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>82.27</v>
       </c>
       <c r="F97" s="9" t="n"/>
-      <c r="K97" s="9" t="n"/>
+      <c r="G97" s="18" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>433.16</v>
+      </c>
+      <c r="I97" s="18" t="n">
+        <v>436.87</v>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>409.98</v>
+      </c>
+      <c r="K97" s="34" t="n">
+        <v>1495.51</v>
+      </c>
+      <c r="L97" s="18" t="n">
+        <v>486.9</v>
+      </c>
+      <c r="M97" s="18" t="n">
+        <v>596.37</v>
+      </c>
       <c r="N97" s="18" t="n">
-        <v>170.15</v>
+        <v>599.65</v>
       </c>
       <c r="O97" s="18" t="n">
-        <v>114.38</v>
-      </c>
-      <c r="P97" s="9" t="n"/>
+        <v>571.97</v>
+      </c>
+      <c r="P97" s="34" t="n">
+        <v>2254.89</v>
+      </c>
       <c r="Q97" s="18" t="n">
-        <v>81.2</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>61.7</v>
+        <v>772.2</v>
       </c>
       <c r="S97" s="18" t="n">
-        <v>81.12</v>
+        <v>772.02</v>
       </c>
       <c r="T97" s="18" t="n">
-        <v>23.16</v>
+        <v>743.35</v>
       </c>
       <c r="U97" s="34" t="n">
-        <v>247.18</v>
+        <v>2938.39</v>
       </c>
       <c r="V97" s="18" t="n">
-        <v>61.62</v>
+        <v>776.3099999999999</v>
       </c>
       <c r="W97" s="18" t="n">
-        <v>119.95</v>
+        <v>788.46</v>
       </c>
       <c r="X97" s="18" t="n">
-        <v>117.69</v>
+        <v>817.3</v>
       </c>
       <c r="Y97" s="18" t="n">
-        <v>672.09</v>
+        <v>779.91</v>
       </c>
       <c r="Z97" s="34" t="n">
-        <v>971.35</v>
+        <v>3161.98</v>
       </c>
       <c r="AA97" s="18" t="n">
-        <v>110.31</v>
-      </c>
-      <c r="AB97" s="19" t="n">
-        <v>547.4400000000001</v>
-      </c>
+        <v>1653.2</v>
+      </c>
+      <c r="AB97" s="5" t="n"/>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
       <c r="AE97" s="11" t="n"/>
@@ -17935,49 +17781,79 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>배당금지급</t>
-        </is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>-74046.17</v>
       </c>
       <c r="F98" s="9" t="n"/>
-      <c r="K98" s="9" t="n"/>
+      <c r="G98" s="18" t="n">
+        <v>89416.61</v>
+      </c>
+      <c r="H98" s="18" t="n">
+        <v>17420.87</v>
+      </c>
+      <c r="I98" s="18" t="n">
+        <v>-57674.06</v>
+      </c>
+      <c r="J98" s="18" t="n">
+        <v>-3097.89</v>
+      </c>
+      <c r="K98" s="34" t="n">
+        <v>46065.53</v>
+      </c>
+      <c r="L98" s="18" t="n">
+        <v>37772.24</v>
+      </c>
+      <c r="M98" s="18" t="n">
+        <v>61348.02</v>
+      </c>
       <c r="N98" s="18" t="n">
-        <v>0</v>
+        <v>-88242.32000000001</v>
       </c>
       <c r="O98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="9" t="n"/>
+        <v>-13725.06</v>
+      </c>
+      <c r="P98" s="34" t="n">
+        <v>-2847.12</v>
+      </c>
       <c r="Q98" s="18" t="n">
-        <v>5602.78</v>
+        <v>29976.44</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>3976.13</v>
+        <v>31445.1</v>
       </c>
       <c r="S98" s="18" t="n">
-        <v>0</v>
+        <v>-47766.46</v>
       </c>
       <c r="T98" s="18" t="n">
-        <v>0</v>
+        <v>12882.78</v>
       </c>
       <c r="U98" s="34" t="n">
-        <v>9578.91</v>
+        <v>26537.86</v>
       </c>
       <c r="V98" s="18" t="n">
-        <v>0</v>
+        <v>47500.22</v>
       </c>
       <c r="W98" s="18" t="n">
-        <v>18644.14</v>
+        <v>-2121.1</v>
       </c>
       <c r="X98" s="18" t="n">
-        <v>0</v>
+        <v>-28996.46</v>
       </c>
       <c r="Y98" s="18" t="n">
-        <v>2.63</v>
+        <v>23395.77</v>
       </c>
       <c r="Z98" s="34" t="n">
-        <v>18646.77</v>
-      </c>
-      <c r="AB98" s="5" t="n"/>
+        <v>39778.43</v>
+      </c>
+      <c r="AA98" s="18" t="n">
+        <v>-31346.36</v>
+      </c>
+      <c r="AB98" s="19" t="n">
+        <v>10168.76</v>
+      </c>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
       <c r="AE98" s="11" t="n"/>
@@ -17991,6 +17867,379 @@
       <c r="AM98" s="10" t="n"/>
       <c r="AN98" s="10" t="n"/>
       <c r="AO98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>-37029.15</v>
+      </c>
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="18" t="n">
+        <v>123601.61</v>
+      </c>
+      <c r="H99" s="18" t="n">
+        <v>8710.360000000001</v>
+      </c>
+      <c r="I99" s="18" t="n">
+        <v>-28837.04</v>
+      </c>
+      <c r="J99" s="18" t="n">
+        <v>-1578.62</v>
+      </c>
+      <c r="K99" s="34" t="n">
+        <v>101896.31</v>
+      </c>
+      <c r="L99" s="18" t="n">
+        <v>120782.43</v>
+      </c>
+      <c r="M99" s="18" t="n">
+        <v>30674.01</v>
+      </c>
+      <c r="N99" s="18" t="n">
+        <v>-44121.16</v>
+      </c>
+      <c r="O99" s="18" t="n">
+        <v>-6862.53</v>
+      </c>
+      <c r="P99" s="34" t="n">
+        <v>100472.75</v>
+      </c>
+      <c r="Q99" s="18" t="n">
+        <v>115460.97</v>
+      </c>
+      <c r="R99" s="18" t="n">
+        <v>15722.55</v>
+      </c>
+      <c r="S99" s="18" t="n">
+        <v>-23883.23</v>
+      </c>
+      <c r="T99" s="18" t="n">
+        <v>6441.39</v>
+      </c>
+      <c r="U99" s="34" t="n">
+        <v>113741.68</v>
+      </c>
+      <c r="V99" s="18" t="n">
+        <v>137491.8</v>
+      </c>
+      <c r="W99" s="18" t="n">
+        <v>-629.89</v>
+      </c>
+      <c r="X99" s="18" t="n">
+        <v>-14498.23</v>
+      </c>
+      <c r="Y99" s="18" t="n">
+        <v>31156.43</v>
+      </c>
+      <c r="Z99" s="34" t="n">
+        <v>153520.11</v>
+      </c>
+      <c r="AA99" s="18" t="n">
+        <v>122173.76</v>
+      </c>
+      <c r="AB99" s="19" t="n">
+        <v>10168.75</v>
+      </c>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="11" t="n"/>
+      <c r="AK99" s="10" t="n"/>
+      <c r="AL99" s="10" t="n"/>
+      <c r="AM99" s="10" t="n"/>
+      <c r="AN99" s="10" t="n"/>
+      <c r="AO99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="n"/>
+      <c r="J100" s="18" t="n">
+        <v>3219.58</v>
+      </c>
+      <c r="K100" s="9" t="n"/>
+      <c r="P100" s="9" t="n"/>
+      <c r="Q100" s="18" t="n">
+        <v>1274.12</v>
+      </c>
+      <c r="S100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" s="18" t="n">
+        <v>1610.69</v>
+      </c>
+      <c r="U100" s="9" t="n"/>
+      <c r="V100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="9" t="n"/>
+      <c r="AB100" s="5" t="n"/>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="11" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="11" t="n"/>
+      <c r="AK100" s="10" t="n"/>
+      <c r="AL100" s="10" t="n"/>
+      <c r="AM100" s="10" t="n"/>
+      <c r="AN100" s="10" t="n"/>
+      <c r="AO100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="n"/>
+      <c r="K101" s="9" t="n"/>
+      <c r="L101" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N101" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="P101" s="9" t="n"/>
+      <c r="S101" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" s="9" t="n"/>
+      <c r="X101" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="9" t="n"/>
+      <c r="AB101" s="5" t="n"/>
+      <c r="AC101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="11" t="n"/>
+      <c r="AK101" s="10" t="n"/>
+      <c r="AL101" s="10" t="n"/>
+      <c r="AM101" s="10" t="n"/>
+      <c r="AN101" s="10" t="n"/>
+      <c r="AO101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="n"/>
+      <c r="K102" s="9" t="n"/>
+      <c r="N102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="9" t="n"/>
+      <c r="Q102" s="18" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="R102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="V102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9" t="n"/>
+      <c r="AB102" s="5" t="n"/>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="10" t="n"/>
+      <c r="AL102" s="10" t="n"/>
+      <c r="AM102" s="10" t="n"/>
+      <c r="AN102" s="10" t="n"/>
+      <c r="AO102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="K103" s="9" t="n"/>
+      <c r="N103" s="18" t="n">
+        <v>170.15</v>
+      </c>
+      <c r="O103" s="18" t="n">
+        <v>114.38</v>
+      </c>
+      <c r="P103" s="9" t="n"/>
+      <c r="Q103" s="18" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="R103" s="18" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="S103" s="18" t="n">
+        <v>81.12</v>
+      </c>
+      <c r="T103" s="18" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="U103" s="34" t="n">
+        <v>247.18</v>
+      </c>
+      <c r="V103" s="18" t="n">
+        <v>61.62</v>
+      </c>
+      <c r="W103" s="18" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="X103" s="18" t="n">
+        <v>117.69</v>
+      </c>
+      <c r="Y103" s="18" t="n">
+        <v>672.09</v>
+      </c>
+      <c r="Z103" s="34" t="n">
+        <v>971.35</v>
+      </c>
+      <c r="AA103" s="18" t="n">
+        <v>110.31</v>
+      </c>
+      <c r="AB103" s="19" t="n">
+        <v>547.4400000000001</v>
+      </c>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="10" t="n"/>
+      <c r="AL103" s="10" t="n"/>
+      <c r="AM103" s="10" t="n"/>
+      <c r="AN103" s="10" t="n"/>
+      <c r="AO103" s="11" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="n"/>
+      <c r="K104" s="9" t="n"/>
+      <c r="N104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="9" t="n"/>
+      <c r="Q104" s="18" t="n">
+        <v>5602.78</v>
+      </c>
+      <c r="R104" s="18" t="n">
+        <v>3976.13</v>
+      </c>
+      <c r="S104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="34" t="n">
+        <v>9578.91</v>
+      </c>
+      <c r="V104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="18" t="n">
+        <v>18644.14</v>
+      </c>
+      <c r="X104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z104" s="34" t="n">
+        <v>18646.77</v>
+      </c>
+      <c r="AB104" s="5" t="n"/>
+      <c r="AC104" s="10" t="n"/>
+      <c r="AD104" s="10" t="n"/>
+      <c r="AE104" s="11" t="n"/>
+      <c r="AF104" s="10" t="n"/>
+      <c r="AG104" s="10" t="n"/>
+      <c r="AH104" s="10" t="n"/>
+      <c r="AI104" s="10" t="n"/>
+      <c r="AJ104" s="11" t="n"/>
+      <c r="AK104" s="10" t="n"/>
+      <c r="AL104" s="10" t="n"/>
+      <c r="AM104" s="10" t="n"/>
+      <c r="AN104" s="10" t="n"/>
+      <c r="AO104" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18251,7 +18500,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28730,31 +28979,67 @@
         <f>IFERROR(VLOOKUP($D21,BS연결,MATCH(X$1,BS연결H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="Y21" s="18" t="n"/>
+      <c r="Y21" s="18">
+        <f>IFERROR(VLOOKUP($D21,BS연결,MATCH(Y$1,BS연결H,0),0)/100,"")</f>
+        <v/>
+      </c>
       <c r="Z21" s="34">
-        <f>Y21</f>
+        <f>IFERROR(VLOOKUP($D21,BS연결,MATCH(Z$1,BS연결H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="AA21" s="18" t="n"/>
-      <c r="AB21" s="19" t="n"/>
-      <c r="AC21" s="20" t="n"/>
-      <c r="AD21" s="20" t="n"/>
+      <c r="AB21" s="19">
+        <f>IFERROR(VLOOKUP($D21,BS연결,MATCH(AB$1,BS연결H,0),0)/100,"")</f>
+        <v/>
+      </c>
+      <c r="AC21" s="20">
+        <f>IFERROR(AB21*(1+변수!AC32),"")</f>
+        <v/>
+      </c>
+      <c r="AD21" s="20">
+        <f>IFERROR(AC21*(1+변수!AD32),"")</f>
+        <v/>
+      </c>
       <c r="AE21" s="35">
         <f>AD21</f>
         <v/>
       </c>
-      <c r="AF21" s="20" t="n"/>
-      <c r="AG21" s="20" t="n"/>
-      <c r="AH21" s="20" t="n"/>
-      <c r="AI21" s="20" t="n"/>
+      <c r="AF21" s="20">
+        <f>IFERROR(AD21*(1+변수!AF32),"")</f>
+        <v/>
+      </c>
+      <c r="AG21" s="20">
+        <f>IFERROR(AF21*(1+변수!AG32),"")</f>
+        <v/>
+      </c>
+      <c r="AH21" s="20">
+        <f>IFERROR(AG21*(1+변수!AH32),"")</f>
+        <v/>
+      </c>
+      <c r="AI21" s="20">
+        <f>IFERROR(AH21*(1+변수!AI32),"")</f>
+        <v/>
+      </c>
       <c r="AJ21" s="35">
         <f>AI21</f>
         <v/>
       </c>
-      <c r="AK21" s="20" t="n"/>
-      <c r="AL21" s="20" t="n"/>
-      <c r="AM21" s="20" t="n"/>
-      <c r="AN21" s="20" t="n"/>
+      <c r="AK21" s="20">
+        <f>IFERROR(AI21*(1+변수!AK32),"")</f>
+        <v/>
+      </c>
+      <c r="AL21" s="20">
+        <f>IFERROR(AK21*(1+변수!AL32),"")</f>
+        <v/>
+      </c>
+      <c r="AM21" s="20">
+        <f>IFERROR(AL21*(1+변수!AM32),"")</f>
+        <v/>
+      </c>
+      <c r="AN21" s="20">
+        <f>IFERROR(AM21*(1+변수!AN32),"")</f>
+        <v/>
+      </c>
       <c r="AO21" s="35">
         <f>AN21</f>
         <v/>
@@ -28855,31 +29140,67 @@
         <f>IFERROR(VLOOKUP($D22,BS연결,MATCH(X$1,BS연결H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="Y22" s="18" t="n"/>
+      <c r="Y22" s="18">
+        <f>IFERROR(VLOOKUP($D22,BS연결,MATCH(Y$1,BS연결H,0),0)/100,"")</f>
+        <v/>
+      </c>
       <c r="Z22" s="34">
-        <f>Y22</f>
+        <f>IFERROR(VLOOKUP($D22,BS연결,MATCH(Z$1,BS연결H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="AA22" s="18" t="n"/>
-      <c r="AB22" s="19" t="n"/>
-      <c r="AC22" s="20" t="n"/>
-      <c r="AD22" s="20" t="n"/>
+      <c r="AB22" s="19">
+        <f>IFERROR(VLOOKUP($D22,BS연결,MATCH(AB$1,BS연결H,0),0)/100,"")</f>
+        <v/>
+      </c>
+      <c r="AC22" s="20">
+        <f>IFERROR(AB22*(1+변수!AC33),"")</f>
+        <v/>
+      </c>
+      <c r="AD22" s="20">
+        <f>IFERROR(AC22*(1+변수!AD33),"")</f>
+        <v/>
+      </c>
       <c r="AE22" s="35">
         <f>AD22</f>
         <v/>
       </c>
-      <c r="AF22" s="20" t="n"/>
-      <c r="AG22" s="20" t="n"/>
-      <c r="AH22" s="20" t="n"/>
-      <c r="AI22" s="20" t="n"/>
+      <c r="AF22" s="20">
+        <f>IFERROR(AD22*(1+변수!AF33),"")</f>
+        <v/>
+      </c>
+      <c r="AG22" s="20">
+        <f>IFERROR(AF22*(1+변수!AG33),"")</f>
+        <v/>
+      </c>
+      <c r="AH22" s="20">
+        <f>IFERROR(AG22*(1+변수!AH33),"")</f>
+        <v/>
+      </c>
+      <c r="AI22" s="20">
+        <f>IFERROR(AH22*(1+변수!AI33),"")</f>
+        <v/>
+      </c>
       <c r="AJ22" s="35">
         <f>AI22</f>
         <v/>
       </c>
-      <c r="AK22" s="20" t="n"/>
-      <c r="AL22" s="20" t="n"/>
-      <c r="AM22" s="20" t="n"/>
-      <c r="AN22" s="20" t="n"/>
+      <c r="AK22" s="20">
+        <f>IFERROR(AI22*(1+변수!AK33),"")</f>
+        <v/>
+      </c>
+      <c r="AL22" s="20">
+        <f>IFERROR(AK22*(1+변수!AL33),"")</f>
+        <v/>
+      </c>
+      <c r="AM22" s="20">
+        <f>IFERROR(AL22*(1+변수!AM33),"")</f>
+        <v/>
+      </c>
+      <c r="AN22" s="20">
+        <f>IFERROR(AM22*(1+변수!AN33),"")</f>
+        <v/>
+      </c>
       <c r="AO22" s="35">
         <f>AN22</f>
         <v/>
@@ -30126,54 +30447,24 @@
       <c r="AB31" s="19" t="n">
         <v>5.84</v>
       </c>
-      <c r="AC31" s="20">
-        <f>IFERROR(X31*(1+변수!AC40),"")</f>
-        <v/>
-      </c>
-      <c r="AD31" s="20">
-        <f>IFERROR(Y31*(1+변수!AD40),"")</f>
-        <v/>
-      </c>
+      <c r="AC31" s="20" t="n"/>
+      <c r="AD31" s="20" t="n"/>
       <c r="AE31" s="35">
         <f>SUM(AA31:AD31)</f>
         <v/>
       </c>
-      <c r="AF31" s="20">
-        <f>IFERROR(AA31*(1+변수!AF40),"")</f>
-        <v/>
-      </c>
-      <c r="AG31" s="20">
-        <f>IFERROR(AB31*(1+변수!AG40),"")</f>
-        <v/>
-      </c>
-      <c r="AH31" s="20">
-        <f>IFERROR(AC31*(1+변수!AH40),"")</f>
-        <v/>
-      </c>
-      <c r="AI31" s="20">
-        <f>IFERROR(AD31*(1+변수!AI40),"")</f>
-        <v/>
-      </c>
+      <c r="AF31" s="20" t="n"/>
+      <c r="AG31" s="20" t="n"/>
+      <c r="AH31" s="20" t="n"/>
+      <c r="AI31" s="20" t="n"/>
       <c r="AJ31" s="35">
         <f>SUM(AF31:AI31)</f>
         <v/>
       </c>
-      <c r="AK31" s="20">
-        <f>IFERROR(AF31*(1+변수!AK40),"")</f>
-        <v/>
-      </c>
-      <c r="AL31" s="20">
-        <f>IFERROR(AG31*(1+변수!AL40),"")</f>
-        <v/>
-      </c>
-      <c r="AM31" s="20">
-        <f>IFERROR(AH31*(1+변수!AM40),"")</f>
-        <v/>
-      </c>
-      <c r="AN31" s="20">
-        <f>IFERROR(AI31*(1+변수!AN40),"")</f>
-        <v/>
-      </c>
+      <c r="AK31" s="20" t="n"/>
+      <c r="AL31" s="20" t="n"/>
+      <c r="AM31" s="20" t="n"/>
+      <c r="AN31" s="20" t="n"/>
       <c r="AO31" s="35">
         <f>SUM(AK31:AN31)</f>
         <v/>
@@ -30288,42 +30579,18 @@
         <f>SUM(AA32:AD32)</f>
         <v/>
       </c>
-      <c r="AF32" s="20">
-        <f>IFERROR(AA32*(1+변수!AF41),"")</f>
-        <v/>
-      </c>
-      <c r="AG32" s="20">
-        <f>IFERROR(AB32*(1+변수!AG41),"")</f>
-        <v/>
-      </c>
-      <c r="AH32" s="20">
-        <f>IFERROR(AC32*(1+변수!AH41),"")</f>
-        <v/>
-      </c>
-      <c r="AI32" s="20">
-        <f>IFERROR(AD32*(1+변수!AI41),"")</f>
-        <v/>
-      </c>
+      <c r="AF32" s="20" t="n"/>
+      <c r="AG32" s="20" t="n"/>
+      <c r="AH32" s="20" t="n"/>
+      <c r="AI32" s="20" t="n"/>
       <c r="AJ32" s="35">
         <f>SUM(AF32:AI32)</f>
         <v/>
       </c>
-      <c r="AK32" s="20">
-        <f>IFERROR(AF32*(1+변수!AK41),"")</f>
-        <v/>
-      </c>
-      <c r="AL32" s="20">
-        <f>IFERROR(AG32*(1+변수!AL41),"")</f>
-        <v/>
-      </c>
-      <c r="AM32" s="20">
-        <f>IFERROR(AH32*(1+변수!AM41),"")</f>
-        <v/>
-      </c>
-      <c r="AN32" s="20">
-        <f>IFERROR(AI32*(1+변수!AN41),"")</f>
-        <v/>
-      </c>
+      <c r="AK32" s="20" t="n"/>
+      <c r="AL32" s="20" t="n"/>
+      <c r="AM32" s="20" t="n"/>
+      <c r="AN32" s="20" t="n"/>
       <c r="AO32" s="35">
         <f>SUM(AK32:AN32)</f>
         <v/>
@@ -38270,7 +38537,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2565.5</v>
+        <v>-18730</v>
       </c>
     </row>
     <row r="30">
@@ -38289,9 +38556,6 @@
           <t>per_now</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>2.94</v>
-      </c>
     </row>
     <row r="32">
       <c r="C32" s="2" t="inlineStr">
@@ -38310,7 +38574,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2567</v>
+        <v>-1.8741</v>
       </c>
     </row>
     <row r="34">
@@ -38319,18 +38583,12 @@
           <t>fair_pbr</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>2.85</v>
-      </c>
     </row>
     <row r="35">
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>fair_value_pbr</t>
         </is>
-      </c>
-      <c r="D35" t="n">
-        <v>28500</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 253980억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 253964억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263158억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 263123억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 272093억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 272040억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283204억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283133억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 298569억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 298498억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 316779억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 316710억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 336299억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 336233억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 355620억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 355558억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 372744억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 372686억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1530,55 +1530,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 253980억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 253964억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263158억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 263123억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 272093억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 272040억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283204억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283133억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 298569억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 298498억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 316779억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 316710억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 336299억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 336233억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 355620억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 355558억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 372744억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 372686억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1938,7 +1938,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3627억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3626억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -1998,7 +1998,7 @@
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3627억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3626억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>7690</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>7950</v>
+        <v>7900</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>8196.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7935</v>
+        <v>7923.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6111,33 +6111,33 @@
         <v>0.249918742</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.413483636</v>
+        <v>0.413392285</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.32935506</v>
+        <v>0.329184559</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.352228382</v>
+        <v>0.351967663</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180949617</v>
+        <v>0.180659392</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175562265</v>
+        <v>0.175356632</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203761969</v>
+        <v>0.203651815</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.23596759</v>
+        <v>0.235962588</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255708907</v>
+        <v>0.255796346</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248434156</v>
+        <v>0.248536886</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6422,39 +6422,39 @@
         <v>0.070675644</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.070675456</v>
+        <v>0.070675407</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.07067419599999999</v>
+        <v>0.070675245</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.070677348</v>
+        <v>0.07067720299999999</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.070674452</v>
+        <v>0.07067707600000001</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.070676013</v>
+        <v>0.070677235</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.070674414</v>
+        <v>0.07067662700000001</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.070673793</v>
+        <v>0.070676563</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.070675085</v>
+        <v>0.070675791</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.07067501299999999</v>
+        <v>0.070676692</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>0.000403402</v>
+        <v>0.000937564</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>-0.005179659</v>
+        <v>-0.003635932</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>-0.00726221</v>
+        <v>-0.004749513</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>216.019551342</v>
+        <v>216.022788671</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>-0.004297954</v>
+        <v>-0.001120235</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>0.002316511</v>
+        <v>0.006526445</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>-0.008700523</v>
+        <v>0.005682008</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>216.018662152</v>
+        <v>216.022087522</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>0.000355266</v>
+        <v>-0.006275489</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>0.002354401</v>
+        <v>0.005958794</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.00632742</v>
+        <v>-0.007141822</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.006408073</v>
+        <v>-0.003141588</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.005075418</v>
+        <v>-0.003293609</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>216.021457693</v>
+        <v>216.024931438</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.009392931</v>
+        <v>0.004156609</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.008404538</v>
+        <v>0.003177355</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.009357738000000001</v>
+        <v>-0.004840668</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>216.021313241</v>
+        <v>216.024493269</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.004434646</v>
+        <v>-0.001181434</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.005804723</v>
+        <v>-0.001292372</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7556,33 +7556,33 @@
         <v>-0.005418311</v>
       </c>
       <c r="AD31" s="24" t="n">
-        <v>-0.00712702</v>
+        <v>-0.007126435</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>-0.00843196</v>
+        <v>-0.008430778</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.005542407</v>
+        <v>0.005544179</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>-0.006696683</v>
+        <v>-0.006694887</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>-0.008713004999999999</v>
+        <v>-0.008710580000000001</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>-0.010564542</v>
+        <v>-0.01056146</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.003638736</v>
+        <v>0.003640515</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>-0.008885057999999999</v>
+        <v>-0.008883736999999999</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>-0.011428801</v>
+        <v>-0.011426813</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7684,33 +7684,33 @@
         <v>0.032824244</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.041576701</v>
+        <v>0.04157329</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.046889225</v>
+        <v>0.046882829</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.029192057</v>
+        <v>-0.029201716</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.036533653</v>
+        <v>0.036524692</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.045551197</v>
+        <v>0.045540036</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.052364458</v>
+        <v>0.052351615</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.016957341</v>
+        <v>-0.01696668</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.042273923</v>
+        <v>0.042267852</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.051707688</v>
+        <v>0.051705595</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>7950</v>
+        <v>7900</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.08413854132099656</v>
+        <v>0.08413325437163625</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1080923251222065</v>
+        <v>0.1080925864798081</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.926747135174305</v>
+        <v>0.926733081317682</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.0004463374003984691</v>
+        <v>0.0004464850234704283</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.004394371108416078</v>
+        <v>0.004394394605154799</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36784,7 +36784,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38772,7 +38772,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1444.3</v>
+        <v>1444.1</v>
       </c>
     </row>
     <row r="30">
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="32">
@@ -38802,7 +38802,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 253964억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 253950억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263123억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 263087억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 272040억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 271982억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283133억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283054억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 298498억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 298412억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 316710억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 316627억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 336233억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 336153억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 355558억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 355482억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 372686억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 372615억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1530,55 +1530,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 253964억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 253950억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263123억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 263087억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 272040억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 271982억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283133억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283054억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 298498억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 298412억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 316710억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 316627억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 336233억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 336153억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 355558억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 355482억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 372686억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 372615억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>7690</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>7900</v>
+        <v>7810</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>8196.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7923.3</v>
+        <v>7895</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6111,33 +6111,33 @@
         <v>0.249918742</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.413392285</v>
+        <v>0.413320509</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.329184559</v>
+        <v>0.328998074</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.351967663</v>
+        <v>0.351675907</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180659392</v>
+        <v>0.180328535</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175356632</v>
+        <v>0.175074677</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203651815</v>
+        <v>0.203503989</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.235962588</v>
+        <v>0.23594004</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255796346</v>
+        <v>0.255882801</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248536886</v>
+        <v>0.248664152</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6422,39 +6422,39 @@
         <v>0.070675644</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.070675407</v>
+        <v>0.07067437999999999</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.070675245</v>
+        <v>0.070677144</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.07067720299999999</v>
+        <v>0.070674088</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.07067707600000001</v>
+        <v>0.070677217</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.070677235</v>
+        <v>0.07067421</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.07067662700000001</v>
+        <v>0.070675239</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.070676563</v>
+        <v>0.070674529</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.070675791</v>
+        <v>0.07067507200000001</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.070676692</v>
+        <v>0.07067430199999999</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>0.000937564</v>
+        <v>0.000251988</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>-0.003635932</v>
+        <v>-0.013685388</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>-0.004749513</v>
+        <v>0.005889619</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>216.022788671</v>
+        <v>216.015262466</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>-0.001120235</v>
+        <v>0.001416794</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>0.006526445</v>
+        <v>-0.009497070999999999</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>0.005682008</v>
+        <v>-0.000557023</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>216.022087522</v>
+        <v>216.025156639</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>-0.006275489</v>
+        <v>-0.003990989</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>0.005958794</v>
+        <v>-0.011209062</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.007141822</v>
+        <v>-0.0065839</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.003141588</v>
+        <v>-0.00089399</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.003293609</v>
+        <v>0.000597198</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>216.024931438</v>
+        <v>216.021725272</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.004156609</v>
+        <v>0.000889631</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.003177355</v>
+        <v>-0.006866004</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.004840668</v>
+        <v>-0.00470493</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>216.024493269</v>
+        <v>216.022997825</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.001181434</v>
+        <v>-0.004250651</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.001292372</v>
+        <v>-0.002603698</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7560,29 +7560,29 @@
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>-0.008430778</v>
+        <v>-0.008429011</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.005544179</v>
+        <v>0.005545951</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>-0.006694887</v>
+        <v>-0.006692501</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>-0.008710580000000001</v>
+        <v>-0.008708149</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>-0.01056146</v>
+        <v>-0.010558372</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.003640515</v>
+        <v>0.003643504</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>-0.008883736999999999</v>
+        <v>-0.008881192</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>-0.011426813</v>
+        <v>-0.011424789</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7684,33 +7684,33 @@
         <v>0.032824244</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.04157329</v>
+        <v>0.041569879</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.046882829</v>
+        <v>0.046876433</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.029201716</v>
+        <v>-0.029211374</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.036524692</v>
+        <v>0.036512509</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.045540036</v>
+        <v>0.045529016</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.052351615</v>
+        <v>0.052338927</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.01696668</v>
+        <v>-0.016981719</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.042267852</v>
+        <v>0.042262144</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.051705595</v>
+        <v>0.051698414</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>7900</v>
+        <v>7810</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,880원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,940원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.08413325437163625</v>
+        <v>0.08413995117982098</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1080925864798081</v>
+        <v>0.1080929465324173</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.926733081317682</v>
+        <v>0.9267458884735115</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.0004464850234704283</v>
+        <v>0.0004466495896944415</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.004394394605154799</v>
+        <v>0.00439442084280894</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36784,7 +36784,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38772,7 +38772,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1444.1</v>
+        <v>1443.9</v>
       </c>
     </row>
     <row r="30">
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.47</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="32">
@@ -38802,7 +38802,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 253950억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 253942억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263087억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 263078억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 271982억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 271973억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283054억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283044억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 298412억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 298410억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 316627억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 316625억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 336153억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 336152억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 355482억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 355481억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 372615억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 372614억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1530,55 +1530,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 253950억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 253942억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263087억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 263078억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 271982억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 271973억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283054억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283044억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 298412억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 298410억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 316627억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 316625억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 336153억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 336152억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 355482억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 355481억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 372615억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 372614억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>7690</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>7810</v>
+        <v>7560</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5865,7 +5865,7 @@
         <v>6880</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>7670</v>
+        <v>7520</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>8196.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7895</v>
+        <v>7822</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6111,33 +6111,33 @@
         <v>0.249918742</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.413320509</v>
+        <v>0.413268309</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.328998074</v>
+        <v>0.328955449</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.351675907</v>
+        <v>0.351632454</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180328535</v>
+        <v>0.180287903</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175074677</v>
+        <v>0.175113463</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203503989</v>
+        <v>0.203538581</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.23594004</v>
+        <v>0.235975181</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255882801</v>
+        <v>0.255921117</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248664152</v>
+        <v>0.248665129</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6422,39 +6422,39 @@
         <v>0.070675644</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.07067437999999999</v>
+        <v>0.07067699</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.070677144</v>
+        <v>0.070675402</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.070674088</v>
+        <v>0.07067635999999999</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.070677217</v>
+        <v>0.070674732</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.07067421</v>
+        <v>0.07067448799999999</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.070675239</v>
+        <v>0.070675474</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.070674529</v>
+        <v>0.070674792</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.07067507200000001</v>
+        <v>0.070675349</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.07067430199999999</v>
+        <v>0.070674525</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>0.000251988</v>
+        <v>8.4995e-05</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>-0.013685388</v>
+        <v>-0.00390439</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>0.005889619</v>
+        <v>-0.003524128</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>216.015262466</v>
+        <v>216.025042507</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>0.001416794</v>
+        <v>-0.007946603</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>-0.009497070999999999</v>
+        <v>-0.009759696999999999</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>-0.000557023</v>
+        <v>-0.000874352</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>216.025156639</v>
+        <v>216.024878028</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>-0.003990989</v>
+        <v>-0.004254237</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>-0.011209062</v>
+        <v>-0.001542972</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.0065839</v>
+        <v>-0.008111564</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.00089399</v>
+        <v>0.007107333</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>0.000597198</v>
+        <v>-0.010235948</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>216.021725272</v>
+        <v>216.019714377</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.000889631</v>
+        <v>0.000542615</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.006866004</v>
+        <v>-0.009267215000000001</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.00470493</v>
+        <v>-0.007592686</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>216.022997825</v>
+        <v>216.020442043</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.004250651</v>
+        <v>-0.006661064</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.002603698</v>
+        <v>-0.005675236</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7556,33 +7556,33 @@
         <v>-0.005418311</v>
       </c>
       <c r="AD31" s="24" t="n">
-        <v>-0.007126435</v>
+        <v>-0.00712585</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>-0.008429011</v>
+        <v>-0.008429005999999999</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.005545951</v>
+        <v>0.005546541</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>-0.006692501</v>
+        <v>-0.006692493</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>-0.008708149</v>
+        <v>-0.008708139</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>-0.010558372</v>
+        <v>-0.01055836</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.003643504</v>
+        <v>0.0036435</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>-0.008881192</v>
+        <v>-0.008881181</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>-0.011424789</v>
+        <v>-0.011424166</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7688,29 +7688,29 @@
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.046876433</v>
+        <v>0.046873158</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.029211374</v>
+        <v>-0.029214594</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.036512509</v>
+        <v>0.036512744</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.045529016</v>
+        <v>0.045529299</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.052338927</v>
+        <v>0.052339239</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.016981719</v>
+        <v>-0.016981814</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.042262144</v>
+        <v>0.042262387</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.051698414</v>
+        <v>0.051695941</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>7810</v>
+        <v>7560</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,940원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,920원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.08413995117982098</v>
+        <v>0.08414159430289932</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1080929465324173</v>
+        <v>0.1080932653961834</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.9267458884735115</v>
+        <v>0.9267311532967071</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.0004466495896944415</v>
+        <v>0.0004466624254500294</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.00439442084280894</v>
+        <v>0.004394422771303082</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36784,7 +36784,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.41</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="32">
@@ -38802,7 +38802,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -657,61 +657,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 239810억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 240366억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 253942억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255228억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263078억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 264589억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 271973억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 273339억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283044억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283443억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 298410억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297493억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 316625억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 314813억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 336152억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 333844억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 355481억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 353088억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 372614억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 370545억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1524,61 +1524,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 239810억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 240366억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 253942억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255228억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263078억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 264589억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 271973억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 273339억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283044억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283443억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 298410억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297493억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 316625억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 314813억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 336152억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 333844억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 355481억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 353088억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 372614억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 370545억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1896,37 +1896,37 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3054억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3055억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3197억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3199억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3103억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3106억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3217억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3219억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3363억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3365억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3539억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3540억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -1938,7 +1938,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3626억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3625억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -1956,37 +1956,37 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3054억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3055억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3197억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3199억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3103억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3106억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3217억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3219억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3363억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3365억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3539억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3540억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -1998,7 +1998,7 @@
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3626억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3625억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -6108,36 +6108,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.249918742</v>
+        <v>0.252820806</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.413268309</v>
+        <v>0.42043282</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.328955449</v>
+        <v>0.336585346</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.351632454</v>
+        <v>0.358423548</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180287903</v>
+        <v>0.179215891</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175113463</v>
+        <v>0.165594036</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203538581</v>
+        <v>0.189819576</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.235975181</v>
+        <v>0.221351442</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255921117</v>
+        <v>0.245709066</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248665129</v>
+        <v>0.245557408</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6419,42 +6419,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.070675644</v>
+        <v>0.070674079</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.07067699</v>
+        <v>0.070674219</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.070675402</v>
+        <v>0.070674576</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.07067635999999999</v>
+        <v>0.070674898</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.070674732</v>
+        <v>0.070673339</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.07067448799999999</v>
+        <v>0.07067554199999999</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.070675474</v>
+        <v>0.070676883</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.070674792</v>
+        <v>0.070677063</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.070675349</v>
+        <v>0.07067728500000001</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.070674525</v>
+        <v>0.070676868</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>8.4995e-05</v>
+        <v>-0.002039199</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>-0.00390439</v>
+        <v>-0.006726054</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>-0.003524128</v>
+        <v>-0.006091281</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>216.025042507</v>
+        <v>216.022427835</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>-0.007946603</v>
+        <v>-0.002704748</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>-0.009759696999999999</v>
+        <v>-0.000830784</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>-0.000874352</v>
+        <v>0.004043532</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>216.024878028</v>
+        <v>216.026929463</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>-0.004254237</v>
+        <v>0.00994866</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>-0.001542972</v>
+        <v>0.005768433</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.008111564</v>
+        <v>-0.007084838</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.007107333</v>
+        <v>0.005154664</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.010235948</v>
+        <v>-0.007601688</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>216.019714377</v>
+        <v>216.027970371</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.000542615</v>
+        <v>-0.005303744</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.009267215000000001</v>
+        <v>-0.000430784</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.007592686</v>
+        <v>0.012122169</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>216.020442043</v>
+        <v>216.022920299</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.006661064</v>
+        <v>0.011756507</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.005675236</v>
+        <v>0.00870542</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7553,36 +7553,36 @@
         <v/>
       </c>
       <c r="AC31" s="24" t="n">
-        <v>-0.005418311</v>
+        <v>-0.005433431</v>
       </c>
       <c r="AD31" s="24" t="n">
-        <v>-0.00712585</v>
+        <v>-0.007167474</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>-0.008429005999999999</v>
+        <v>-0.008484258999999999</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.005546541</v>
+        <v>0.005504995</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>-0.006692493</v>
+        <v>-0.006704158</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>-0.008708139</v>
+        <v>-0.008679254000000001</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>-0.01055836</v>
+        <v>-0.010493213</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.0036435</v>
+        <v>0.003715906</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>-0.008881181</v>
+        <v>-0.008813517999999999</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>-0.011424166</v>
+        <v>-0.0113539</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7681,36 +7681,36 @@
         <v/>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.032824244</v>
+        <v>0.032915841</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.041569879</v>
+        <v>0.041808353</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.046873158</v>
+        <v>0.047162739</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.029214594</v>
+        <v>-0.028975267</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.036512744</v>
+        <v>0.036540016</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.045529299</v>
+        <v>0.045331428</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.052339239</v>
+        <v>0.051973946</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.016981814</v>
+        <v>-0.017312337</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.042262387</v>
+        <v>0.041940695</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.051695941</v>
+        <v>0.051397705</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.08414159430289932</v>
+        <v>0.08412604236619571</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1080932653961834</v>
+        <v>0.108093100848925</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.9267311532967071</v>
+        <v>0.9267530433544529</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.0004466624254500294</v>
+        <v>0.0004471080417214843</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.004394422771303082</v>
+        <v>0.004394526730242884</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38772,7 +38772,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1443.9</v>
+        <v>1451.7</v>
       </c>
     </row>
     <row r="30">
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.24</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="32">
@@ -38812,7 +38812,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1445</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255228억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255226억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 264589억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 264609억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 273339억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 273380억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283443억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283505억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297493억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297576억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 314813억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 314894억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 333844억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 333921억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 353088억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 353161억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 370545억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 370614억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1530,55 +1530,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255228억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255226억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 264589억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 264609억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 273339억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 273380억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283443억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283505억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297493억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297576억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 314813억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 314894억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 333844억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 333921억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 353088억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 353161억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 370545억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 370614억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>7690</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>7560</v>
+        <v>7580</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>8196.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7822</v>
+        <v>7826</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6111,33 +6111,33 @@
         <v>0.252820806</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.42043282</v>
+        <v>0.42041977</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.336585346</v>
+        <v>0.336686581</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.358423548</v>
+        <v>0.35862219</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179215891</v>
+        <v>0.179470697</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165594036</v>
+        <v>0.165930901</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189819576</v>
+        <v>0.190036393</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221351442</v>
+        <v>0.221456149</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245709066</v>
+        <v>0.245695263</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245557408</v>
+        <v>0.245441436</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6422,39 +6422,39 @@
         <v>0.070674079</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.070674219</v>
+        <v>0.070674868</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.070674576</v>
+        <v>0.070677195</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.070674898</v>
+        <v>0.070673703</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.070673339</v>
+        <v>0.070677711</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.07067554199999999</v>
+        <v>0.070675471</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.070676883</v>
+        <v>0.070675402</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.070677063</v>
+        <v>0.070675634</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.07067728500000001</v>
+        <v>0.07067462300000001</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.070676868</v>
+        <v>0.07067633</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>-0.002039199</v>
+        <v>-0.002407122</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>-0.006726054</v>
+        <v>-0.007213839</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>-0.006091281</v>
+        <v>0.001648052</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>216.022427835</v>
+        <v>216.020247887</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>-0.002704748</v>
+        <v>0.003477253</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>-0.000830784</v>
+        <v>-0.005621264</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>0.004043532</v>
+        <v>-0.000861695</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>216.026929463</v>
+        <v>216.022944128</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>0.00994866</v>
+        <v>0.006845759</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>0.005768433</v>
+        <v>0.001661887</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.007084838</v>
+        <v>-0.008105655</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.005154664</v>
+        <v>0.003810702</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.007601688</v>
+        <v>-0.00221005</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>216.027970371</v>
+        <v>216.023587522</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.005303744</v>
+        <v>-0.002598021</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.000430784</v>
+        <v>0.000405014</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.012122169</v>
+        <v>0.002640789</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>216.022920299</v>
+        <v>216.025170788</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.011756507</v>
+        <v>-0.004378512</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.00870542</v>
+        <v>0.010613792</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7560,29 +7560,29 @@
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>-0.008484258999999999</v>
+        <v>-0.008484848</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.005504995</v>
+        <v>0.00550381</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>-0.006704158</v>
+        <v>-0.006705942</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>-0.008679254000000001</v>
+        <v>-0.008682258</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>-0.010493213</v>
+        <v>-0.010496282</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.003715906</v>
+        <v>0.003713517</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>-0.008813517999999999</v>
+        <v>-0.008815437000000001</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>-0.0113539</v>
+        <v>-0.011356496</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7688,29 +7688,29 @@
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.047162739</v>
+        <v>0.047166012</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.028975267</v>
+        <v>-0.028968924</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.036540016</v>
+        <v>0.036549322</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.045331428</v>
+        <v>0.045346114</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.051973946</v>
+        <v>0.051984133</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.017312337</v>
+        <v>-0.017297481</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.041940695</v>
+        <v>0.041946907</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.051397705</v>
+        <v>0.051405478</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>7560</v>
+        <v>7580</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,920원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,890원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.08412604236619571</v>
+        <v>0.08412969505755967</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.108093100848925</v>
+        <v>0.1080923872968486</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.9267530433544529</v>
+        <v>0.9267457668135262</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.0004471080417214843</v>
+        <v>0.0004469675745220452</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.004394526730242884</v>
+        <v>0.004394504093217351</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1451.7</v>
+        <v>1451.8</v>
       </c>
     </row>
     <row r="30">
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255226억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255224억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 264609억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 264597억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 273380억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 273359억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283505억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283476억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297576억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297542억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 314894억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 314861억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 333921억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 333890억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 353161억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 353131억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 370614억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 370586억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1530,55 +1530,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255226억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255224억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 264609억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 264597억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 273380억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 273359억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283505억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283476억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297576억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297542억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 314894억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 314861억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 333921억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 333890억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 353161억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 353131억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 370614억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 370586억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6111,33 +6111,33 @@
         <v>0.252820806</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.42041977</v>
+        <v>0.420400195</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.336686581</v>
+        <v>0.336627971</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.35862219</v>
+        <v>0.358522869</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179470697</v>
+        <v>0.179349085</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165930901</v>
+        <v>0.165809155</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.190036393</v>
+        <v>0.189961014</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221456149</v>
+        <v>0.221431215</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245695263</v>
+        <v>0.245720599</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245441436</v>
+        <v>0.245494093</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6422,39 +6422,39 @@
         <v>0.070674079</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.070674868</v>
+        <v>0.070675842</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.070677195</v>
+        <v>0.07067630799999999</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.070673703</v>
+        <v>0.07067430099999999</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.070677711</v>
+        <v>0.07067517800000001</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.070675471</v>
+        <v>0.070675945</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.070675402</v>
+        <v>0.07067627899999999</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.070675634</v>
+        <v>0.070674762</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.07067462300000001</v>
+        <v>0.070676532</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.07067633</v>
+        <v>0.070675369</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>-0.002407122</v>
+        <v>-0.003248214</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>-0.007213839</v>
+        <v>-0.008315355999999999</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>0.001648052</v>
+        <v>0.001196828</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>216.020247887</v>
+        <v>216.019984364</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>0.003477253</v>
+        <v>-0.00586045</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>-0.005621264</v>
+        <v>0.004751038</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>-0.000861695</v>
+        <v>-0.000749372</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>216.022944128</v>
+        <v>216.013237856</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>0.006845759</v>
+        <v>0.006375593</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>0.001661887</v>
+        <v>0.001670152</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.008105655</v>
+        <v>-0.009469740000000001</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.003810702</v>
+        <v>0.002022913</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.00221005</v>
+        <v>-0.002797105</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>216.023587522</v>
+        <v>216.023304013</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.002598021</v>
+        <v>-0.011229381</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.000405014</v>
+        <v>0.001301789</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.002640789</v>
+        <v>0.00311533</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>216.025170788</v>
+        <v>216.015939753</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.004378512</v>
+        <v>0.005005143</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.010613792</v>
+        <v>0.000920611</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7560,29 +7560,29 @@
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>-0.008484848</v>
+        <v>-0.008484258999999999</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.00550381</v>
+        <v>0.005504401</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>-0.006705942</v>
+        <v>-0.006705344</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>-0.008682258</v>
+        <v>-0.008680459</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>-0.010496282</v>
+        <v>-0.010495044</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.003713517</v>
+        <v>0.003714105</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>-0.008815437000000001</v>
+        <v>-0.008814785</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>-0.011356496</v>
+        <v>-0.011355208</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7688,29 +7688,29 @@
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.047166012</v>
+        <v>0.047162739</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.028968924</v>
+        <v>-0.028972141</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.036549322</v>
+        <v>0.036546337</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.045346114</v>
+        <v>0.045337218</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.051984133</v>
+        <v>0.051982088</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.017297481</v>
+        <v>-0.017303472</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.041946907</v>
+        <v>0.041945118</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.051405478</v>
+        <v>0.051401379</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.08412969505755967</v>
+        <v>0.08413792204236234</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1080923872968486</v>
+        <v>0.1080922979840186</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.9267457668135262</v>
+        <v>0.9267395095561805</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.0004469675745220452</v>
+        <v>0.0004470305891805159</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.004394504093217351</v>
+        <v>0.004394514186712548</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38772,7 +38772,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1451.8</v>
+        <v>1451.7</v>
       </c>
     </row>
     <row r="30">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         <v>7690</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>7580</v>
+        <v>7240</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5865,7 +5865,7 @@
         <v>6880</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>7520</v>
+        <v>7150</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>8196.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7826</v>
+        <v>7728.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>7580</v>
+        <v>7240</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36784,7 +36784,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.22</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="32">
@@ -38802,7 +38802,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255224억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255216억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 264597억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 264551억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 273359억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 273274억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283476억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283347억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297542억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297378억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 314861억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 314695억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 333890억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 333725억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 353131억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 352973억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 370586억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 370436억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1530,55 +1530,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255224억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255216억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 264597억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 264551억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 273359억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 273274억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283476억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283347억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297542억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297378억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 314861억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 314695억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 333890억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 333725억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 353131억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 352973억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 370586억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 370436억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>7690</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>7240</v>
+        <v>7120</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5865,7 +5865,7 @@
         <v>6880</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>7150</v>
+        <v>6800</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>8196.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7728.3</v>
+        <v>7640</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6111,33 +6111,33 @@
         <v>0.252820806</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.420400195</v>
+        <v>0.420361044</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.336627971</v>
+        <v>0.336393533</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.358522869</v>
+        <v>0.358094546</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179349085</v>
+        <v>0.178810517</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165809155</v>
+        <v>0.165198137</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189961014</v>
+        <v>0.189543813</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221431215</v>
+        <v>0.221213091</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245720599</v>
+        <v>0.245729697</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245494093</v>
+        <v>0.24567691</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6422,39 +6422,39 @@
         <v>0.070674079</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.070675842</v>
+        <v>0.07067779</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.07067630799999999</v>
+        <v>0.070676746</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.07067430099999999</v>
+        <v>0.070673736</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.07067517800000001</v>
+        <v>0.070677992</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.070675945</v>
+        <v>0.07067553</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.07067627899999999</v>
+        <v>0.07067660100000001</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.070674762</v>
+        <v>0.07067599400000001</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.070676532</v>
+        <v>0.07067675700000001</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.070675369</v>
+        <v>0.07067551599999999</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>-0.003248214</v>
+        <v>-0.002624295</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>-0.008315355999999999</v>
+        <v>0.002512161</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>0.001196828</v>
+        <v>-0.005297618</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>216.019984364</v>
+        <v>216.02503769</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>-0.00586045</v>
+        <v>-4.2462e-05</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>0.004751038</v>
+        <v>-0.0058435</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>-0.000749372</v>
+        <v>0.009693762</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>216.013237856</v>
+        <v>216.021863837</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>0.006375593</v>
+        <v>0.004085613</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>0.001670152</v>
+        <v>0.000498534</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.009469740000000001</v>
+        <v>-0.008294469</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.002022913</v>
+        <v>0.003573105</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.002797105</v>
+        <v>0.0035699</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>216.023304013</v>
+        <v>216.022438136</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.011229381</v>
+        <v>-0.000716989</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.001301789</v>
+        <v>-0.001723538</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.00311533</v>
+        <v>0.001969362</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>216.015939753</v>
+        <v>216.031515666</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.005005143</v>
+        <v>-0.001056692</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.000920611</v>
+        <v>0.006885902</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7556,33 +7556,33 @@
         <v>-0.005433431</v>
       </c>
       <c r="AD31" s="24" t="n">
-        <v>-0.007167474</v>
+        <v>-0.007166889</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>-0.008484258999999999</v>
+        <v>-0.008483076000000001</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.005504401</v>
+        <v>0.005507361</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>-0.006705344</v>
+        <v>-0.006701768</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>-0.008680459</v>
+        <v>-0.008675629000000001</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>-0.010495044</v>
+        <v>-0.010488306</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.003714105</v>
+        <v>0.003719487</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>-0.008814785</v>
+        <v>-0.008810333</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>-0.011355208</v>
+        <v>-0.011349994</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7684,33 +7684,33 @@
         <v>0.032915841</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.041808353</v>
+        <v>0.041804942</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.047162739</v>
+        <v>0.047156345</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.028972141</v>
+        <v>-0.028988045</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.036546337</v>
+        <v>0.03652796</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.045337218</v>
+        <v>0.045314339</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.051982088</v>
+        <v>0.051952799</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.017303472</v>
+        <v>-0.017330508</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.041945118</v>
+        <v>0.041930059</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.051401379</v>
+        <v>0.051386256</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>7240</v>
+        <v>7120</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,890원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,560원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.08413792204236234</v>
+        <v>0.08413171504783769</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1080922979840186</v>
+        <v>0.1080924796561476</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.9267395095561805</v>
+        <v>0.9267459000633771</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.0004470305891805159</v>
+        <v>0.0004473260626706207</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.004394514186712548</v>
+        <v>0.004394561660596782</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36784,7 +36784,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38772,7 +38772,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1451.7</v>
+        <v>1451.5</v>
       </c>
     </row>
     <row r="30">
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.99</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="32">
@@ -38802,7 +38802,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="33">
@@ -38812,7 +38812,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1453</v>
+        <v>0.1452</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255216억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255215억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 264551억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 264588억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 273274억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 273348억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283347억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283457억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297378억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297524억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 314695억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 314836억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 333725억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 333860억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 352973억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 353102억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 370436억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 370556억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1530,55 +1530,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255216억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255215억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 264551억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 264588억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 273274억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 273348억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283347억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283457억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297378억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297524억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 314695억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 314836억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 333725억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 333860억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 352973억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 353102억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 370436억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 370556억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>7690</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>7120</v>
+        <v>7320</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>8196.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7640</v>
+        <v>7598.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6111,33 +6111,33 @@
         <v>0.252820806</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.420361044</v>
+        <v>0.420354519</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.336393533</v>
+        <v>0.336580018</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.358094546</v>
+        <v>0.358467001</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.178810517</v>
+        <v>0.17926801</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165198137</v>
+        <v>0.165777735</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189543813</v>
+        <v>0.18991202</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221213091</v>
+        <v>0.221371778</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245729697</v>
+        <v>0.245698207</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.24567691</v>
+        <v>0.245465257</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6422,39 +6422,39 @@
         <v>0.070674079</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.07067779</v>
+        <v>0.070673521</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.070676746</v>
+        <v>0.07067485699999999</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.070673736</v>
+        <v>0.07067720700000001</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.070677992</v>
+        <v>0.070675126</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.07067553</v>
+        <v>0.070676182</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.07067660100000001</v>
+        <v>0.070675024</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.07067599400000001</v>
+        <v>0.070677367</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.07067675700000001</v>
+        <v>0.07067477699999999</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.07067551599999999</v>
+        <v>0.07067485499999999</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>-0.002624295</v>
+        <v>-0.002478632</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>0.002512161</v>
+        <v>-0.006462831</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>-0.005297618</v>
+        <v>-0.006774136</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>216.02503769</v>
+        <v>216.021002326</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>-4.2462e-05</v>
+        <v>0.005916307</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>-0.0058435</v>
+        <v>-0.00320403</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>0.009693762</v>
+        <v>0.002376014</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>216.021863837</v>
+        <v>216.025357353</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>0.004085613</v>
+        <v>-0.000740375</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>0.000498534</v>
+        <v>-0.005111737</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.008294469</v>
+        <v>-0.009811419</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.003573105</v>
+        <v>-0.006911504</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>0.0035699</v>
+        <v>-0.001810575</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>216.022438136</v>
+        <v>216.02285468</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.000716989</v>
+        <v>-0.000131634</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.001723538</v>
+        <v>-0.00771844</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.001969362</v>
+        <v>0.005501961</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>216.031515666</v>
+        <v>216.016889395</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.001056692</v>
+        <v>-0.002504431</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.006885902</v>
+        <v>0.003264546</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7560,29 +7560,29 @@
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>-0.008483076000000001</v>
+        <v>-0.008484254</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.005507361</v>
+        <v>0.005504398</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>-0.006701768</v>
+        <v>-0.006704158</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>-0.008675629000000001</v>
+        <v>-0.008680442999999999</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>-0.010488306</v>
+        <v>-0.010493825</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.003719487</v>
+        <v>0.003715306</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>-0.008810333</v>
+        <v>-0.008814143999999999</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>-0.011349994</v>
+        <v>-0.011354544</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7688,29 +7688,29 @@
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.047156345</v>
+        <v>0.047162893</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.028988045</v>
+        <v>-0.028975358</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.03652796</v>
+        <v>0.036543353</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.045314339</v>
+        <v>0.045337641</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.051952799</v>
+        <v>0.051976609</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.017330508</v>
+        <v>-0.017309365</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.041930059</v>
+        <v>0.041943087</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.051386256</v>
+        <v>0.051399755</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>7120</v>
+        <v>7320</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,560원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,210원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.08413171504783769</v>
+        <v>0.08413036816815644</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1080924796561476</v>
+        <v>0.1080927487689308</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.9267459000633771</v>
+        <v>0.9267282188543321</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.0004473260626706207</v>
+        <v>0.0004470753341855459</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.004394561660596782</v>
+        <v>0.004394521280834037</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36784,7 +36784,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38772,7 +38772,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1451.5</v>
+        <v>1451.7</v>
       </c>
     </row>
     <row r="30">
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.91</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="32">
@@ -38802,7 +38802,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="33">
@@ -38812,7 +38812,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1452</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255215억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255574억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 264588억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 265188억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 273348억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 273966억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283457억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 283920억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297524억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297343억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 314836억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 314042억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 333860억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 332644억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 353102억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 351658억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 370556억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 369082억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1530,55 +1530,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255215억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255574억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 264588억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 265188억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 273348억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 273966억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283457억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 283920억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297524억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297343억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 314836억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 314042억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 333860억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 332644억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 353102억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 351658억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 370556억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 369082억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1908,25 +1908,25 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3106억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3107억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3219억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3221억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3365억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3366억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3540억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3541억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -1938,7 +1938,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3625억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3624억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -1968,25 +1968,25 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3106억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3107억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3219억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3221억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3365억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3366억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3540억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3541억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -1998,7 +1998,7 @@
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3625억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3624억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>7690</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>7320</v>
+        <v>7050</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5865,7 +5865,7 @@
         <v>6880</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>6800</v>
+        <v>6580</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>8196.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7598.8</v>
+        <v>7408.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6111,33 +6111,33 @@
         <v>0.252820806</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.420354519</v>
+        <v>0.422351186</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.336580018</v>
+        <v>0.33961173</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.358467001</v>
+        <v>0.361539753</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.17926801</v>
+        <v>0.181196433</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165777735</v>
+        <v>0.163434763</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.18991202</v>
+        <v>0.184224133</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221371778</v>
+        <v>0.214179224</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245698207</v>
+        <v>0.238585275</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245465257</v>
+        <v>0.241265097</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6422,39 +6422,39 @@
         <v>0.070674079</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.070673521</v>
+        <v>0.070675236</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.07067485699999999</v>
+        <v>0.070674006</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.07067720700000001</v>
+        <v>0.070677274</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.070675126</v>
+        <v>0.070677407</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.070676182</v>
+        <v>0.07067572499999999</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.070675024</v>
+        <v>0.07067575700000001</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.070677367</v>
+        <v>0.0706765</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.07067477699999999</v>
+        <v>0.070675644</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.07067485499999999</v>
+        <v>0.070674341</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>-0.002478632</v>
+        <v>-0.0029563</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>-0.006462831</v>
+        <v>-0.005579114</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>-0.006774136</v>
+        <v>-0.00110563</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>216.021002326</v>
+        <v>216.021013901</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>0.005916307</v>
+        <v>-0.00474124</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>-0.00320403</v>
+        <v>0.005464305</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>0.002376014</v>
+        <v>-0.003755851</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>216.025357353</v>
+        <v>216.022738248</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>-0.000740375</v>
+        <v>-2.1845e-05</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>-0.005111737</v>
+        <v>-0.001178301</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.009811419</v>
+        <v>-0.009452914</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.006911504</v>
+        <v>0.000305841</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.001810575</v>
+        <v>-0.001696825</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>216.02285468</v>
+        <v>216.020478945</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.000131634</v>
+        <v>0.004114342</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.00771844</v>
+        <v>-0.000374608</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.005501961</v>
+        <v>-0.003514324</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>216.016889395</v>
+        <v>216.021944973</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.002504431</v>
+        <v>-0.001500903</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.003264546</v>
+        <v>-0.00141667</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7556,33 +7556,33 @@
         <v>-0.005433431</v>
       </c>
       <c r="AD31" s="24" t="n">
-        <v>-0.007166889</v>
+        <v>-0.007178583</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>-0.008484254</v>
+        <v>-0.008505555999999999</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.005504398</v>
+        <v>0.005485573</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>-0.006704158</v>
+        <v>-0.006718094</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>-0.008680442999999999</v>
+        <v>-0.008674474</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>-0.010493825</v>
+        <v>-0.010465657</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.003715306</v>
+        <v>0.00375362</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>-0.008814143999999999</v>
+        <v>-0.008773615</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>-0.011354544</v>
+        <v>-0.011304035</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7684,33 +7684,33 @@
         <v>0.032915841</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.041804942</v>
+        <v>0.041873156</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.047162893</v>
+        <v>0.047277656</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.028975358</v>
+        <v>-0.028867133</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.036543353</v>
+        <v>0.036603697</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.045337641</v>
+        <v>0.045287858</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.051976609</v>
+        <v>0.051818581</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.017309365</v>
+        <v>-0.017484749</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.041943087</v>
+        <v>0.041751823</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.051399755</v>
+        <v>0.051184557</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>7320</v>
+        <v>7050</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,210원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,750원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.08413036816815644</v>
+        <v>0.08413453693369102</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1080927487689308</v>
+        <v>0.1080923362330385</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.9267282188543321</v>
+        <v>0.9267367940933322</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.0004470753341855459</v>
+        <v>0.000447269778001765</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.004394521280834037</v>
+        <v>0.004394563443425542</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36784,7 +36784,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38772,7 +38772,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1451.7</v>
+        <v>1454.4</v>
       </c>
     </row>
     <row r="30">
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.04</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="32">
@@ -38802,7 +38802,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="33">
@@ -38812,7 +38812,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1453</v>
+        <v>0.1455</v>
       </c>
     </row>
     <row r="34">
@@ -38822,7 +38822,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="35">
@@ -38832,7 +38832,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16100</v>
+        <v>16200</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/064820_model.xlsx
+++ b/argus/kship/models/064820_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 255574억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 255852억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 265188억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 265700억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 273966억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 274541억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 283920억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 284424억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297343억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 297400억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 314042억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 313630억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 332644억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 331909억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 351658억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 350749억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 369082억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 368148억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1530,55 +1530,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 255574억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255852억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 265188억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 265700억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 273966억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 274541억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 283920억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 284424억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297343억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297400억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 314042억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 313630억 × 비례계수 0.0332 × 계절비중 Q1 0.286(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 332644억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 331909억 × 비례계수 0.0332 × 계절비중 Q2 0.241(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 351658억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 350749억 × 비례계수 0.0332 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 369082억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 368148억 × 비례계수 0.0332 × 계절비중 Q4 0.257(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.94, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1902,31 +1902,31 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3199억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3200억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3107억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3108억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3221억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3222억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3366억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3367억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3541억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 3542억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -1962,31 +1962,31 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3199억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3200억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3107억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3108억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3221억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3222억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3366억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3367억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 3541억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 3542억 × 0.04%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 18519억 × 0.44%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>7690</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>7050</v>
+        <v>6560</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5865,7 +5865,7 @@
         <v>6880</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>6580</v>
+        <v>6110</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>8196.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7408.2</v>
+        <v>7146.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6111,33 +6111,33 @@
         <v>0.252820806</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.422351186</v>
+        <v>0.42390415</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.33961173</v>
+        <v>0.342201206</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.361539753</v>
+        <v>0.36439524</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.181196433</v>
+        <v>0.183298587</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.163434763</v>
+        <v>0.162385838</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.184224133</v>
+        <v>0.180391254</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.214179224</v>
+        <v>0.208958348</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.238585275</v>
+        <v>0.23318423</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.241265097</v>
+        <v>0.237892114</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6422,39 +6422,39 @@
         <v>0.070674079</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.070675236</v>
+        <v>0.070676058</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.070674006</v>
+        <v>0.07067659599999999</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.070677274</v>
+        <v>0.070674947</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.070677407</v>
+        <v>0.07067419699999999</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.07067572499999999</v>
+        <v>0.070674178</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.07067575700000001</v>
+        <v>0.07067429</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.0706765</v>
+        <v>0.070675102</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.070675644</v>
+        <v>0.070676525</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.070674341</v>
+        <v>0.070675159</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>-0.0029563</v>
+        <v>-0.002350939</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>-0.005579114</v>
+        <v>0.000920151</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>-0.00110563</v>
+        <v>0.000406516</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>216.021013901</v>
+        <v>216.014936012</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>-0.00474124</v>
+        <v>-0.004963669</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>0.005464305</v>
+        <v>0.003987087</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>-0.003755851</v>
+        <v>-0.00896097</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>216.022738248</v>
+        <v>216.019138015</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>-2.1845e-05</v>
+        <v>0.009646411000000001</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>-0.001178301</v>
+        <v>-0.002873965</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.009452914</v>
+        <v>-0.008813936</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.000305841</v>
+        <v>0.005442046</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.001696825</v>
+        <v>-0.003618904</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>216.020478945</v>
+        <v>216.02297083</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.004114342</v>
+        <v>-0.002847241</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.000374608</v>
+        <v>-0.003819756</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.003514324</v>
+        <v>0.000123057</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>216.021944973</v>
+        <v>216.01657681</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.001500903</v>
+        <v>-0.000916934</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.00141667</v>
+        <v>0.004530503</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7556,33 +7556,33 @@
         <v>-0.005433431</v>
       </c>
       <c r="AD31" s="24" t="n">
-        <v>-0.007178583</v>
+        <v>-0.007187354</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>-0.008505555999999999</v>
+        <v>-0.008524477000000001</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.005485573</v>
+        <v>0.005467905</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>-0.006718094</v>
+        <v>-0.006731988</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>-0.008674474</v>
+        <v>-0.008676774</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>-0.010465657</v>
+        <v>-0.010451304</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.00375362</v>
+        <v>0.003776839</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>-0.008773615</v>
+        <v>-0.008747853</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>-0.011304035</v>
+        <v>-0.011272936</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7684,33 +7684,33 @@
         <v>0.032915841</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.041873156</v>
+        <v>0.041924317</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.047277656</v>
+        <v>0.047380085</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>-0.028867133</v>
+        <v>-0.028769131</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.036603697</v>
+        <v>0.03666864</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.045287858</v>
+        <v>0.045283113</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.051818581</v>
+        <v>0.05172849</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>-0.017484749</v>
+        <v>-0.017591019</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.041751823</v>
+        <v>0.041626428</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.051184557</v>
+        <v>0.051044256</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>7050</v>
+        <v>6560</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,750원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,510원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.08413453693369102</v>
+        <v>0.08412832115549114</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1080923362330385</v>
+        <v>0.1080919888391991</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.9267367940933322</v>
+        <v>0.9267376285977056</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.000447269778001765</v>
+        <v>0.0004470725480114462</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.004394563443425542</v>
+        <v>0.004394539986208072</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36784,7 +36784,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38772,7 +38772,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1454.4</v>
+        <v>1456.7</v>
       </c>
     </row>
     <row r="30">
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="32">
@@ -38802,7 +38802,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="33">
@@ -38812,7 +38812,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1455</v>
+        <v>0.1458</v>
       </c>
     </row>
     <row r="34">
